--- a/premise/data/additional_inventories/lci-carbon-capture.xlsx
+++ b/premise/data/additional_inventories/lci-carbon-capture.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10720"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/Github/premise/premise/data/additional_inventories/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/GitHub/premise/premise/data/additional_inventories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4F2CD5-055C-3F46-AA42-8D857D2E85C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA28BFAD-10F0-114B-A8B4-C331D85F0120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="44800" windowHeight="22980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34920" yWindow="80" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DAC" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DAC!$A$1:$V$620</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DAC!$A$1:$V$621</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2637" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2642" uniqueCount="322">
   <si>
     <t>Activity</t>
   </si>
@@ -629,6 +629,9 @@
   </si>
   <si>
     <t>concrete, normal strength</t>
+  </si>
+  <si>
+    <t>market for spent anion exchange resin from potable water production</t>
   </si>
   <si>
     <t>Originally 3.7 MJ, without heat recovery. 0.4 MJ using heat from teh MSWI plant. However, when doing so, 40% of teh heat is lost and cannot be redistributed to the heating district system. Hence, we add this loss to the amount of external heat needed.</t>
@@ -1009,14 +1012,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="0.0E+00"/>
-    <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
-    <numFmt numFmtId="169" formatCode="0.0000"/>
-    <numFmt numFmtId="170" formatCode="_ * #,##0.0000_ ;_ * \-#,##0.0000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="171" formatCode="0.00000"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="0.0E+00"/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="_ * #,##0.0000_ ;_ * \-#,##0.0000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="170" formatCode="0.00000"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -1136,13 +1139,13 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1152,29 +1155,29 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="11" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1184,11 +1187,9 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1504,7 +1505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V657"/>
+  <dimension ref="A1:V658"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="47.33203125" customWidth="1"/>
@@ -1537,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
@@ -1553,7 +1554,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
@@ -1633,10 +1634,10 @@
         <v>173</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M12" s="5" t="s">
         <v>182</v>
@@ -1660,7 +1661,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
@@ -1881,7 +1882,7 @@
         <v>78</v>
       </c>
       <c r="H21" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I21">
         <v>5</v>
@@ -1899,7 +1900,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B22">
         <v>6.28</v>
@@ -1917,7 +1918,7 @@
         <v>162</v>
       </c>
       <c r="H22" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I22">
         <v>5</v>
@@ -1958,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
@@ -1974,7 +1975,7 @@
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
@@ -2054,10 +2055,10 @@
         <v>173</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L34" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M34" s="5" t="s">
         <v>182</v>
@@ -2065,7 +2066,7 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -2080,7 +2081,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
@@ -2301,7 +2302,7 @@
         <v>78</v>
       </c>
       <c r="H43" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I43">
         <v>5</v>
@@ -2319,7 +2320,7 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B44">
         <v>6.28</v>
@@ -2337,7 +2338,7 @@
         <v>162</v>
       </c>
       <c r="H44" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I44">
         <v>5</v>
@@ -2401,7 +2402,7 @@
         <v>0</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
@@ -2417,7 +2418,7 @@
         <v>2</v>
       </c>
       <c r="B50" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.2">
@@ -2497,10 +2498,10 @@
         <v>173</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L57" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M57" s="5" t="s">
         <v>182</v>
@@ -2508,7 +2509,7 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -2523,7 +2524,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.2">
@@ -2744,7 +2745,7 @@
         <v>78</v>
       </c>
       <c r="H66" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I66">
         <v>5</v>
@@ -2780,7 +2781,7 @@
         <v>188</v>
       </c>
       <c r="H67" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I67">
         <v>5</v>
@@ -2821,7 +2822,7 @@
         <v>0</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.2">
@@ -2837,7 +2838,7 @@
         <v>2</v>
       </c>
       <c r="B72" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.2">
@@ -2917,10 +2918,10 @@
         <v>173</v>
       </c>
       <c r="K79" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L79" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M79" s="5" t="s">
         <v>182</v>
@@ -2928,7 +2929,7 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -2943,7 +2944,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.2">
@@ -3164,7 +3165,7 @@
         <v>78</v>
       </c>
       <c r="H88" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I88">
         <v>5</v>
@@ -3200,7 +3201,7 @@
         <v>188</v>
       </c>
       <c r="H89" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I89">
         <v>5</v>
@@ -3264,7 +3265,7 @@
         <v>0</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.2">
@@ -3280,7 +3281,7 @@
         <v>2</v>
       </c>
       <c r="B95" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.2">
@@ -3360,10 +3361,10 @@
         <v>173</v>
       </c>
       <c r="K102" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L102" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M102" s="5" t="s">
         <v>182</v>
@@ -3371,7 +3372,7 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -3386,7 +3387,7 @@
         <v>15</v>
       </c>
       <c r="G103" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.2">
@@ -3607,7 +3608,7 @@
         <v>78</v>
       </c>
       <c r="H111" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I111">
         <v>5</v>
@@ -3644,7 +3645,7 @@
         <v>78</v>
       </c>
       <c r="H112" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I112">
         <v>5</v>
@@ -3687,7 +3688,7 @@
         <v>0</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.2">
@@ -3703,7 +3704,7 @@
         <v>2</v>
       </c>
       <c r="B117" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.2">
@@ -3783,10 +3784,10 @@
         <v>173</v>
       </c>
       <c r="K124" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L124" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M124" s="5" t="s">
         <v>182</v>
@@ -3794,7 +3795,7 @@
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -3809,7 +3810,7 @@
         <v>15</v>
       </c>
       <c r="G125" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.2">
@@ -4030,7 +4031,7 @@
         <v>78</v>
       </c>
       <c r="H133" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I133">
         <v>5</v>
@@ -4067,7 +4068,7 @@
         <v>78</v>
       </c>
       <c r="H134" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I134">
         <v>5</v>
@@ -4181,7 +4182,7 @@
         <v>9</v>
       </c>
       <c r="B144" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
@@ -4644,65 +4645,65 @@
     </row>
     <row r="166" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B166">
         <f>78380*20</f>
         <v>1567600</v>
       </c>
       <c r="D166" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E166" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F166" t="s">
         <v>20</v>
       </c>
       <c r="H166" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="167" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B167">
         <f>78380</f>
         <v>78380</v>
       </c>
       <c r="D167" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E167" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F167" t="s">
         <v>20</v>
       </c>
       <c r="H167" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="168" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B168">
         <f>78380</f>
         <v>78380</v>
       </c>
       <c r="D168" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E168" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F168" t="s">
         <v>20</v>
       </c>
       <c r="H168" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="169" spans="1:19" ht="16" x14ac:dyDescent="0.2">
@@ -5004,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="191" spans="1:19" x14ac:dyDescent="0.2">
@@ -5020,7 +5021,7 @@
         <v>2</v>
       </c>
       <c r="B192" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.2">
@@ -5100,10 +5101,10 @@
         <v>173</v>
       </c>
       <c r="K199" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L199" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M199" s="5" t="s">
         <v>182</v>
@@ -5111,7 +5112,7 @@
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -5126,7 +5127,7 @@
         <v>15</v>
       </c>
       <c r="G200" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="201" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -5265,7 +5266,7 @@
         <v>78</v>
       </c>
       <c r="H204" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I204">
         <v>5</v>
@@ -5282,7 +5283,7 @@
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B205">
         <v>5.4</v>
@@ -5300,7 +5301,7 @@
         <v>162</v>
       </c>
       <c r="H205" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I205">
         <v>5</v>
@@ -5340,7 +5341,7 @@
         <v>0</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="209" spans="1:13" x14ac:dyDescent="0.2">
@@ -5356,7 +5357,7 @@
         <v>2</v>
       </c>
       <c r="B210" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="211" spans="1:13" x14ac:dyDescent="0.2">
@@ -5388,7 +5389,7 @@
         <v>9</v>
       </c>
       <c r="B214" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="215" spans="1:13" x14ac:dyDescent="0.2">
@@ -5396,7 +5397,7 @@
         <v>18</v>
       </c>
       <c r="B215" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="216" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -5436,10 +5437,10 @@
         <v>173</v>
       </c>
       <c r="K217" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L217" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M217" s="5" t="s">
         <v>182</v>
@@ -5447,7 +5448,7 @@
     </row>
     <row r="218" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -5462,7 +5463,7 @@
         <v>15</v>
       </c>
       <c r="G218" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="219" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -5601,7 +5602,7 @@
         <v>78</v>
       </c>
       <c r="H222" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I222">
         <v>5</v>
@@ -5618,7 +5619,7 @@
     </row>
     <row r="223" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B223">
         <v>5.4</v>
@@ -5636,7 +5637,7 @@
         <v>162</v>
       </c>
       <c r="H223" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I223">
         <v>5</v>
@@ -5699,7 +5700,7 @@
         <v>0</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.2">
@@ -5715,7 +5716,7 @@
         <v>2</v>
       </c>
       <c r="B229" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.2">
@@ -5795,10 +5796,10 @@
         <v>173</v>
       </c>
       <c r="K236" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L236" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M236" s="5" t="s">
         <v>182</v>
@@ -5806,7 +5807,7 @@
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B237">
         <v>1</v>
@@ -5821,7 +5822,7 @@
         <v>15</v>
       </c>
       <c r="G237" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="238" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -5960,7 +5961,7 @@
         <v>78</v>
       </c>
       <c r="H241" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I241">
         <v>5</v>
@@ -5977,7 +5978,7 @@
     </row>
     <row r="242" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B242">
         <v>5.4</v>
@@ -5992,10 +5993,10 @@
         <v>16</v>
       </c>
       <c r="G242" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H242" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I242">
         <v>5</v>
@@ -6035,7 +6036,7 @@
         <v>0</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="246" spans="1:13" x14ac:dyDescent="0.2">
@@ -6051,7 +6052,7 @@
         <v>2</v>
       </c>
       <c r="B247" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="248" spans="1:13" x14ac:dyDescent="0.2">
@@ -6083,7 +6084,7 @@
         <v>9</v>
       </c>
       <c r="B251" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="252" spans="1:13" x14ac:dyDescent="0.2">
@@ -6091,7 +6092,7 @@
         <v>18</v>
       </c>
       <c r="B252" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="253" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -6131,10 +6132,10 @@
         <v>173</v>
       </c>
       <c r="K254" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L254" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M254" s="5" t="s">
         <v>182</v>
@@ -6142,7 +6143,7 @@
     </row>
     <row r="255" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B255">
         <v>1</v>
@@ -6157,7 +6158,7 @@
         <v>15</v>
       </c>
       <c r="G255" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="256" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -6296,7 +6297,7 @@
         <v>78</v>
       </c>
       <c r="H259" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I259">
         <v>5</v>
@@ -6313,7 +6314,7 @@
     </row>
     <row r="260" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B260">
         <v>5.4</v>
@@ -6328,10 +6329,10 @@
         <v>16</v>
       </c>
       <c r="G260" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H260" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I260">
         <v>5</v>
@@ -6394,7 +6395,7 @@
         <v>0</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="265" spans="1:13" x14ac:dyDescent="0.2">
@@ -6410,7 +6411,7 @@
         <v>2</v>
       </c>
       <c r="B266" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="267" spans="1:13" x14ac:dyDescent="0.2">
@@ -6490,10 +6491,10 @@
         <v>173</v>
       </c>
       <c r="K273" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L273" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M273" s="5" t="s">
         <v>182</v>
@@ -6501,7 +6502,7 @@
     </row>
     <row r="274" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B274">
         <v>1</v>
@@ -6516,7 +6517,7 @@
         <v>15</v>
       </c>
       <c r="G274" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="275" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -6655,7 +6656,7 @@
         <v>78</v>
       </c>
       <c r="H278" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I278">
         <v>5</v>
@@ -6690,7 +6691,7 @@
         <v>188</v>
       </c>
       <c r="H279" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I279">
         <v>5</v>
@@ -6730,7 +6731,7 @@
         <v>0</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="283" spans="1:13" x14ac:dyDescent="0.2">
@@ -6746,7 +6747,7 @@
         <v>2</v>
       </c>
       <c r="B284" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="285" spans="1:13" x14ac:dyDescent="0.2">
@@ -6778,7 +6779,7 @@
         <v>9</v>
       </c>
       <c r="B288" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="289" spans="1:13" x14ac:dyDescent="0.2">
@@ -6786,7 +6787,7 @@
         <v>18</v>
       </c>
       <c r="B289" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="290" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -6826,10 +6827,10 @@
         <v>173</v>
       </c>
       <c r="K291" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L291" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M291" s="5" t="s">
         <v>182</v>
@@ -6837,7 +6838,7 @@
     </row>
     <row r="292" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B292">
         <v>1</v>
@@ -6852,7 +6853,7 @@
         <v>15</v>
       </c>
       <c r="G292" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="293" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -6991,7 +6992,7 @@
         <v>78</v>
       </c>
       <c r="H296" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I296">
         <v>5</v>
@@ -7026,7 +7027,7 @@
         <v>188</v>
       </c>
       <c r="H297" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I297">
         <v>5</v>
@@ -7089,7 +7090,7 @@
         <v>0</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="302" spans="1:13" x14ac:dyDescent="0.2">
@@ -7105,7 +7106,7 @@
         <v>2</v>
       </c>
       <c r="B303" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="304" spans="1:13" x14ac:dyDescent="0.2">
@@ -7185,10 +7186,10 @@
         <v>173</v>
       </c>
       <c r="K310" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L310" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M310" s="5" t="s">
         <v>182</v>
@@ -7196,7 +7197,7 @@
     </row>
     <row r="311" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B311">
         <v>1</v>
@@ -7211,7 +7212,7 @@
         <v>15</v>
       </c>
       <c r="G311" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="312" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -7350,7 +7351,7 @@
         <v>78</v>
       </c>
       <c r="H315" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I315">
         <v>5</v>
@@ -7386,7 +7387,7 @@
         <v>78</v>
       </c>
       <c r="H316" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I316">
         <v>5</v>
@@ -7429,7 +7430,7 @@
         <v>0</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="320" spans="1:13" x14ac:dyDescent="0.2">
@@ -7445,7 +7446,7 @@
         <v>2</v>
       </c>
       <c r="B321" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="322" spans="1:13" x14ac:dyDescent="0.2">
@@ -7477,7 +7478,7 @@
         <v>9</v>
       </c>
       <c r="B325" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="326" spans="1:13" x14ac:dyDescent="0.2">
@@ -7485,7 +7486,7 @@
         <v>18</v>
       </c>
       <c r="B326" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="327" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -7525,10 +7526,10 @@
         <v>173</v>
       </c>
       <c r="K328" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L328" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M328" s="5" t="s">
         <v>182</v>
@@ -7536,7 +7537,7 @@
     </row>
     <row r="329" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B329">
         <v>1</v>
@@ -7551,7 +7552,7 @@
         <v>15</v>
       </c>
       <c r="G329" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="330" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -7690,7 +7691,7 @@
         <v>78</v>
       </c>
       <c r="H333" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I333">
         <v>5</v>
@@ -7726,7 +7727,7 @@
         <v>78</v>
       </c>
       <c r="H334" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I334">
         <v>5</v>
@@ -7840,15 +7841,15 @@
         <v>9</v>
       </c>
       <c r="B344" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>18</v>
       </c>
-      <c r="B345" s="41" t="s">
-        <v>221</v>
+      <c r="B345" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="346" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -7906,7 +7907,7 @@
       <c r="A349" t="s">
         <v>194</v>
       </c>
-      <c r="B349" s="40">
+      <c r="B349">
         <v>8000</v>
       </c>
       <c r="C349" t="s">
@@ -7929,7 +7930,7 @@
       <c r="A350" t="s">
         <v>103</v>
       </c>
-      <c r="B350" s="40">
+      <c r="B350">
         <v>942000</v>
       </c>
       <c r="C350" t="s">
@@ -7952,7 +7953,7 @@
       <c r="A351" t="s">
         <v>194</v>
       </c>
-      <c r="B351" s="40">
+      <c r="B351">
         <v>6000</v>
       </c>
       <c r="C351" t="s">
@@ -7975,7 +7976,7 @@
       <c r="A352" t="s">
         <v>103</v>
       </c>
-      <c r="B352" s="40">
+      <c r="B352">
         <v>548000.00000000012</v>
       </c>
       <c r="C352" t="s">
@@ -7998,7 +7999,7 @@
       <c r="A353" t="s">
         <v>42</v>
       </c>
-      <c r="B353" s="40">
+      <c r="B353">
         <v>120000</v>
       </c>
       <c r="C353" t="s">
@@ -8021,7 +8022,7 @@
       <c r="A354" t="s">
         <v>115</v>
       </c>
-      <c r="B354" s="40">
+      <c r="B354">
         <v>16000</v>
       </c>
       <c r="C354" t="s">
@@ -8044,7 +8045,7 @@
       <c r="A355" t="s">
         <v>59</v>
       </c>
-      <c r="B355" s="40">
+      <c r="B355">
         <v>276000.00000000006</v>
       </c>
       <c r="C355" t="s">
@@ -8067,7 +8068,7 @@
       <c r="A356" t="s">
         <v>43</v>
       </c>
-      <c r="B356" s="40">
+      <c r="B356">
         <v>224000</v>
       </c>
       <c r="C356" t="s">
@@ -8090,7 +8091,7 @@
       <c r="A357" t="s">
         <v>115</v>
       </c>
-      <c r="B357" s="40">
+      <c r="B357">
         <v>10000</v>
       </c>
       <c r="C357" t="s">
@@ -8113,7 +8114,7 @@
       <c r="A358" t="s">
         <v>116</v>
       </c>
-      <c r="B358" s="40">
+      <c r="B358">
         <v>12000</v>
       </c>
       <c r="C358" t="s">
@@ -8136,7 +8137,7 @@
       <c r="A359" t="s">
         <v>152</v>
       </c>
-      <c r="B359" s="40">
+      <c r="B359">
         <v>10000</v>
       </c>
       <c r="C359" t="s">
@@ -8159,7 +8160,7 @@
       <c r="A360" t="s">
         <v>58</v>
       </c>
-      <c r="B360" s="40">
+      <c r="B360">
         <v>160000</v>
       </c>
       <c r="C360" t="s">
@@ -8182,7 +8183,7 @@
       <c r="A361" t="s">
         <v>117</v>
       </c>
-      <c r="B361" s="40">
+      <c r="B361">
         <v>10000</v>
       </c>
       <c r="C361" t="s">
@@ -8205,7 +8206,7 @@
       <c r="A362" t="s">
         <v>43</v>
       </c>
-      <c r="B362" s="40">
+      <c r="B362">
         <v>338000</v>
       </c>
       <c r="C362" t="s">
@@ -8228,7 +8229,7 @@
       <c r="A363" t="s">
         <v>42</v>
       </c>
-      <c r="B363" s="40">
+      <c r="B363">
         <v>28000</v>
       </c>
       <c r="C363" t="s">
@@ -8251,7 +8252,7 @@
       <c r="A364" t="s">
         <v>121</v>
       </c>
-      <c r="B364" s="40">
+      <c r="B364">
         <v>94000</v>
       </c>
       <c r="C364" t="s">
@@ -8274,7 +8275,7 @@
       <c r="A365" t="s">
         <v>116</v>
       </c>
-      <c r="B365" s="40">
+      <c r="B365">
         <v>10000</v>
       </c>
       <c r="C365" t="s">
@@ -8297,7 +8298,7 @@
       <c r="A366" t="s">
         <v>152</v>
       </c>
-      <c r="B366" s="40">
+      <c r="B366">
         <v>10000</v>
       </c>
       <c r="C366" t="s">
@@ -8320,7 +8321,7 @@
       <c r="A367" t="s">
         <v>43</v>
       </c>
-      <c r="B367" s="40">
+      <c r="B367">
         <v>22000</v>
       </c>
       <c r="C367" t="s">
@@ -8343,7 +8344,7 @@
       <c r="A368" t="s">
         <v>42</v>
       </c>
-      <c r="B368" s="40">
+      <c r="B368">
         <v>12000</v>
       </c>
       <c r="C368" t="s">
@@ -8364,65 +8365,65 @@
     </row>
     <row r="369" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B369">
         <f>7838*20</f>
         <v>156760</v>
       </c>
       <c r="D369" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E369" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F369" t="s">
         <v>20</v>
       </c>
       <c r="H369" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="370" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B370">
         <f>7838</f>
         <v>7838</v>
       </c>
       <c r="D370" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E370" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F370" t="s">
         <v>20</v>
       </c>
       <c r="H370" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="371" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B371">
         <f>7838</f>
         <v>7838</v>
       </c>
       <c r="D371" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E371" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F371" t="s">
         <v>20</v>
       </c>
       <c r="H371" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="372" spans="1:19" x14ac:dyDescent="0.2">
@@ -8489,7 +8490,7 @@
         <v>18</v>
       </c>
       <c r="B380" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="381" spans="1:19" ht="16" x14ac:dyDescent="0.2">
@@ -8547,9 +8548,8 @@
       <c r="A384" t="s">
         <v>65</v>
       </c>
-      <c r="B384" s="11">
-        <f>-1*(B349+B351)*2200</f>
-        <v>-30800000</v>
+      <c r="B384">
+        <v>-29400000</v>
       </c>
       <c r="C384" t="s">
         <v>131</v>
@@ -8557,7 +8557,6 @@
       <c r="D384" t="s">
         <v>6</v>
       </c>
-      <c r="E384" s="11"/>
       <c r="F384" t="s">
         <v>16</v>
       </c>
@@ -8572,8 +8571,7 @@
         <v>66</v>
       </c>
       <c r="B385">
-        <f>-1*(B350+B352+B353+B355+B362+B363+B367+B368)</f>
-        <v>-2286000</v>
+        <v>-2140000</v>
       </c>
       <c r="C385" t="s">
         <v>21</v>
@@ -8595,7 +8593,6 @@
         <v>67</v>
       </c>
       <c r="B386">
-        <f>-1*(B358+B364+B365)</f>
         <v>-116000</v>
       </c>
       <c r="C386" t="s">
@@ -8618,8 +8615,7 @@
         <v>72</v>
       </c>
       <c r="B387">
-        <f>-1*(B360)</f>
-        <v>-160000</v>
+        <v>-143999.99999999997</v>
       </c>
       <c r="C387" t="s">
         <v>8</v>
@@ -8636,14 +8632,13 @@
     </row>
     <row r="388" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>110</v>
+        <v>197</v>
       </c>
       <c r="B388">
-        <f>-1*(B359+B366)</f>
-        <v>-20000</v>
+        <v>-6000000</v>
       </c>
       <c r="C388" t="s">
-        <v>131</v>
+        <v>26</v>
       </c>
       <c r="D388" t="s">
         <v>6</v>
@@ -8652,16 +8647,15 @@
         <v>16</v>
       </c>
       <c r="G388" t="s">
-        <v>151</v>
+        <v>27</v>
       </c>
     </row>
     <row r="389" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="B389">
-        <f>-1*(B357+B354)</f>
-        <v>-26000</v>
+        <v>-20000</v>
       </c>
       <c r="C389" t="s">
         <v>131</v>
@@ -8673,133 +8667,133 @@
         <v>16</v>
       </c>
       <c r="G389" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="390" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A390" t="s">
+        <v>130</v>
+      </c>
+      <c r="B390">
+        <v>-26000</v>
+      </c>
+      <c r="C390" t="s">
+        <v>131</v>
+      </c>
+      <c r="D390" t="s">
+        <v>6</v>
+      </c>
+      <c r="F390" t="s">
+        <v>16</v>
+      </c>
+      <c r="G390" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="390" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="G390" s="7"/>
-    </row>
     <row r="391" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A391" s="1" t="s">
+      <c r="G391" s="7"/>
+    </row>
+    <row r="392" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A392" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B391" s="1" t="s">
+      <c r="B392" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="392" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A392" t="s">
-        <v>1</v>
-      </c>
-      <c r="B392">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="393" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
+        <v>1</v>
+      </c>
+      <c r="B393">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A394" t="s">
         <v>2</v>
       </c>
-      <c r="B393" s="7" t="s">
+      <c r="B394" s="7" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="394" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A394" t="s">
-        <v>3</v>
-      </c>
-      <c r="B394" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="395" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B395" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="396" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B396" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="397" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B397" t="s">
-        <v>170</v>
+        <v>8</v>
       </c>
     </row>
     <row r="398" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
+        <v>9</v>
+      </c>
+      <c r="B398" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="399" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A399" t="s">
         <v>18</v>
       </c>
-      <c r="B398" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="399" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A399" s="1" t="s">
+      <c r="B399" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="400" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A400" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="400" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A400" t="s">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A401" t="s">
         <v>11</v>
       </c>
-      <c r="B400" t="s">
+      <c r="B401" t="s">
         <v>12</v>
       </c>
-      <c r="C400" t="s">
+      <c r="C401" t="s">
         <v>7</v>
       </c>
-      <c r="D400" t="s">
-        <v>5</v>
-      </c>
-      <c r="E400" t="s">
+      <c r="D401" t="s">
+        <v>5</v>
+      </c>
+      <c r="E401" t="s">
         <v>13</v>
       </c>
-      <c r="F400" t="s">
+      <c r="F401" t="s">
         <v>3</v>
       </c>
-      <c r="G400" t="s">
+      <c r="G401" t="s">
         <v>2</v>
       </c>
-      <c r="H400" t="s">
+      <c r="H401" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="401" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A401" t="s">
-        <v>79</v>
-      </c>
-      <c r="B401">
-        <v>1</v>
-      </c>
-      <c r="C401" t="s">
-        <v>8</v>
-      </c>
-      <c r="D401" t="s">
-        <v>6</v>
-      </c>
-      <c r="F401" t="s">
-        <v>15</v>
-      </c>
-      <c r="G401" s="7" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="402" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>211</v>
+        <v>79</v>
       </c>
       <c r="B402">
-        <v>0.36</v>
+        <v>1</v>
       </c>
       <c r="C402" t="s">
         <v>8</v>
@@ -8808,343 +8802,329 @@
         <v>6</v>
       </c>
       <c r="F402" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G402" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="H402" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
     </row>
     <row r="403" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B403">
+        <v>0.36</v>
+      </c>
+      <c r="C403" t="s">
+        <v>8</v>
+      </c>
+      <c r="D403" t="s">
+        <v>6</v>
+      </c>
+      <c r="F403" t="s">
+        <v>16</v>
+      </c>
+      <c r="G403" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="H403" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="404" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A404" t="s">
+        <v>218</v>
+      </c>
+      <c r="B404">
         <v>0.64</v>
       </c>
-      <c r="C403" t="s">
-        <v>8</v>
-      </c>
-      <c r="D403" t="s">
-        <v>6</v>
-      </c>
-      <c r="F403" t="s">
-        <v>16</v>
-      </c>
-      <c r="G403" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="H403" t="s">
+      <c r="C404" t="s">
+        <v>8</v>
+      </c>
+      <c r="D404" t="s">
+        <v>6</v>
+      </c>
+      <c r="F404" t="s">
+        <v>16</v>
+      </c>
+      <c r="G404" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="H404" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A404" t="s">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A405" t="s">
         <v>25</v>
       </c>
-      <c r="B404">
+      <c r="B405">
         <v>-1</v>
       </c>
-      <c r="C404" t="s">
+      <c r="C405" t="s">
         <v>26</v>
       </c>
-      <c r="D404" t="s">
-        <v>6</v>
-      </c>
-      <c r="F404" t="s">
-        <v>16</v>
-      </c>
-      <c r="G404" t="s">
+      <c r="D405" t="s">
+        <v>6</v>
+      </c>
+      <c r="F405" t="s">
+        <v>16</v>
+      </c>
+      <c r="G405" t="s">
         <v>27</v>
       </c>
-      <c r="H404" t="s">
+      <c r="H405" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="405" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A405" s="2"/>
-      <c r="J405" s="2"/>
-    </row>
     <row r="406" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A406" s="1" t="s">
+      <c r="A406" s="2"/>
+      <c r="J406" s="2"/>
+    </row>
+    <row r="407" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A407" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B406" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A407" t="s">
-        <v>1</v>
-      </c>
-      <c r="B407">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="408" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="B407" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="408" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
+        <v>1</v>
+      </c>
+      <c r="B408">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A409" t="s">
         <v>2</v>
       </c>
-      <c r="B408" s="22" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A409" t="s">
-        <v>3</v>
-      </c>
-      <c r="B409" t="s">
-        <v>4</v>
+      <c r="B409" s="22" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="410" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B410" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="411" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B411" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="412" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B412" t="s">
-        <v>214</v>
+        <v>8</v>
       </c>
     </row>
     <row r="413" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
+        <v>9</v>
+      </c>
+      <c r="B413" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="414" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A414" t="s">
         <v>18</v>
       </c>
-      <c r="B413" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="414" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A414" s="1" t="s">
+      <c r="B414" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="415" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A415" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A415" s="5" t="s">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A416" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B415" s="5" t="s">
+      <c r="B416" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C415" s="5" t="s">
+      <c r="C416" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D415" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E415" s="5" t="s">
+      <c r="D416" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E416" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F415" s="5" t="s">
+      <c r="F416" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G415" s="5" t="s">
+      <c r="G416" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H415" s="5" t="s">
+      <c r="H416" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I415" s="5" t="s">
+      <c r="I416" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="J415" s="5" t="s">
+      <c r="J416" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="K415" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="L415" s="5" t="s">
+      <c r="K416" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="M415" s="5" t="s">
+      <c r="L416" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="M416" s="5" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="416" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A416" t="str">
-        <f>B406</f>
+    <row r="417" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A417" t="str">
+        <f>B407</f>
         <v>polyethyleneimine (PEI) production, for sorbent-based direct air capture system</v>
       </c>
-      <c r="B416">
-        <v>1</v>
-      </c>
-      <c r="C416" t="s">
-        <v>8</v>
-      </c>
-      <c r="D416" t="s">
-        <v>6</v>
-      </c>
-      <c r="F416" t="s">
+      <c r="B417">
+        <v>1</v>
+      </c>
+      <c r="C417" t="s">
+        <v>8</v>
+      </c>
+      <c r="D417" t="s">
+        <v>6</v>
+      </c>
+      <c r="F417" t="s">
         <v>15</v>
       </c>
-      <c r="G416" s="7" t="str">
-        <f>B408</f>
+      <c r="G417" s="7" t="str">
+        <f>B409</f>
         <v>polyethyleneimine</v>
-      </c>
-    </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A417" t="s">
-        <v>90</v>
-      </c>
-      <c r="B417" s="38">
-        <f t="shared" ref="B417:B427" si="0">AVERAGE(K417:L417)</f>
-        <v>1.9749999999999999</v>
-      </c>
-      <c r="C417" t="s">
-        <v>17</v>
-      </c>
-      <c r="D417" t="s">
-        <v>6</v>
-      </c>
-      <c r="F417" t="s">
-        <v>16</v>
-      </c>
-      <c r="G417" t="s">
-        <v>141</v>
-      </c>
-      <c r="I417">
-        <v>5</v>
-      </c>
-      <c r="J417">
-        <f>B417</f>
-        <v>1.9749999999999999</v>
-      </c>
-      <c r="K417">
-        <v>1.42</v>
-      </c>
-      <c r="L417">
-        <v>2.5299999999999998</v>
       </c>
     </row>
     <row r="418" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
+        <v>90</v>
+      </c>
+      <c r="B418" s="38">
+        <f t="shared" ref="B418:B428" si="0">AVERAGE(K418:L418)</f>
+        <v>1.9749999999999999</v>
+      </c>
+      <c r="C418" t="s">
+        <v>17</v>
+      </c>
+      <c r="D418" t="s">
+        <v>6</v>
+      </c>
+      <c r="F418" t="s">
+        <v>16</v>
+      </c>
+      <c r="G418" t="s">
+        <v>141</v>
+      </c>
+      <c r="I418">
+        <v>5</v>
+      </c>
+      <c r="J418">
+        <f>B418</f>
+        <v>1.9749999999999999</v>
+      </c>
+      <c r="K418">
+        <v>1.42</v>
+      </c>
+      <c r="L418">
+        <v>2.5299999999999998</v>
+      </c>
+    </row>
+    <row r="419" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A419" t="s">
         <v>82</v>
       </c>
-      <c r="B418">
+      <c r="B419">
         <f t="shared" si="0"/>
         <v>3.1749999999999998</v>
       </c>
-      <c r="C418" t="s">
+      <c r="C419" t="s">
         <v>26</v>
       </c>
-      <c r="D418" t="s">
-        <v>6</v>
-      </c>
-      <c r="F418" t="s">
-        <v>16</v>
-      </c>
-      <c r="G418" t="s">
+      <c r="D419" t="s">
+        <v>6</v>
+      </c>
+      <c r="F419" t="s">
+        <v>16</v>
+      </c>
+      <c r="G419" t="s">
         <v>87</v>
       </c>
-      <c r="I418">
-        <v>5</v>
-      </c>
-      <c r="J418">
-        <f t="shared" ref="J418:J427" si="1">B418</f>
+      <c r="I419">
+        <v>5</v>
+      </c>
+      <c r="J419">
+        <f t="shared" ref="J419:J428" si="1">B419</f>
         <v>3.1749999999999998</v>
       </c>
-      <c r="K418">
+      <c r="K419">
         <v>2.2799999999999998</v>
       </c>
-      <c r="L418">
+      <c r="L419">
         <v>4.07</v>
       </c>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A419" t="s">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A420" t="s">
         <v>91</v>
       </c>
-      <c r="B419">
+      <c r="B420">
         <f t="shared" si="0"/>
         <v>2.59</v>
       </c>
-      <c r="C419" t="s">
+      <c r="C420" t="s">
         <v>17</v>
       </c>
-      <c r="D419" t="s">
-        <v>6</v>
-      </c>
-      <c r="F419" t="s">
-        <v>16</v>
-      </c>
-      <c r="G419" t="s">
+      <c r="D420" t="s">
+        <v>6</v>
+      </c>
+      <c r="F420" t="s">
+        <v>16</v>
+      </c>
+      <c r="G420" t="s">
         <v>142</v>
       </c>
-      <c r="I419">
-        <v>5</v>
-      </c>
-      <c r="J419">
+      <c r="I420">
+        <v>5</v>
+      </c>
+      <c r="J420">
         <f t="shared" si="1"/>
         <v>2.59</v>
       </c>
-      <c r="K419">
+      <c r="K420">
         <v>1.86</v>
       </c>
-      <c r="L419">
+      <c r="L420">
         <v>3.32</v>
-      </c>
-    </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A420" t="s">
-        <v>92</v>
-      </c>
-      <c r="B420">
-        <f t="shared" si="0"/>
-        <v>0.19500000000000001</v>
-      </c>
-      <c r="C420" t="s">
-        <v>26</v>
-      </c>
-      <c r="D420" t="s">
-        <v>6</v>
-      </c>
-      <c r="F420" t="s">
-        <v>16</v>
-      </c>
-      <c r="G420" t="s">
-        <v>143</v>
-      </c>
-      <c r="I420">
-        <v>5</v>
-      </c>
-      <c r="J420">
-        <f t="shared" si="1"/>
-        <v>0.19500000000000001</v>
-      </c>
-      <c r="K420">
-        <v>0.16</v>
-      </c>
-      <c r="L420">
-        <v>0.23</v>
       </c>
     </row>
     <row r="421" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B421">
         <f t="shared" si="0"/>
         <v>0.19500000000000001</v>
       </c>
       <c r="C421" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D421" t="s">
         <v>6</v>
@@ -9153,7 +9133,7 @@
         <v>16</v>
       </c>
       <c r="G421" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I421">
         <v>5</v>
@@ -9171,11 +9151,11 @@
     </row>
     <row r="422" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B422">
         <f t="shared" si="0"/>
-        <v>0.11570000000000008</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="C422" t="s">
         <v>17</v>
@@ -9187,366 +9167,378 @@
         <v>16</v>
       </c>
       <c r="G422" t="s">
-        <v>144</v>
-      </c>
-      <c r="H422" t="s">
-        <v>220</v>
+        <v>142</v>
       </c>
       <c r="I422">
         <v>5</v>
       </c>
       <c r="J422">
         <f t="shared" si="1"/>
+        <v>0.19500000000000001</v>
+      </c>
+      <c r="K422">
+        <v>0.16</v>
+      </c>
+      <c r="L422">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="423" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A423" t="s">
+        <v>93</v>
+      </c>
+      <c r="B423">
+        <f t="shared" si="0"/>
         <v>0.11570000000000008</v>
       </c>
-      <c r="K422">
+      <c r="C423" t="s">
+        <v>17</v>
+      </c>
+      <c r="D423" t="s">
+        <v>6</v>
+      </c>
+      <c r="F423" t="s">
+        <v>16</v>
+      </c>
+      <c r="G423" t="s">
+        <v>144</v>
+      </c>
+      <c r="H423" t="s">
+        <v>221</v>
+      </c>
+      <c r="I423">
+        <v>5</v>
+      </c>
+      <c r="J423">
+        <f t="shared" si="1"/>
+        <v>0.11570000000000008</v>
+      </c>
+      <c r="K423">
         <f>2.84*(1-99%)</f>
         <v>2.8400000000000022E-2</v>
       </c>
-      <c r="L422">
+      <c r="L423">
         <f>4.06*(1-95%)</f>
         <v>0.20300000000000015</v>
       </c>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A423" t="s">
+    <row r="424" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A424" t="s">
         <v>94</v>
       </c>
-      <c r="B423">
+      <c r="B424">
         <f t="shared" si="0"/>
         <v>1.3817000000000013</v>
       </c>
-      <c r="C423" t="s">
+      <c r="C424" t="s">
         <v>26</v>
       </c>
-      <c r="D423" t="s">
-        <v>6</v>
-      </c>
-      <c r="F423" t="s">
-        <v>16</v>
-      </c>
-      <c r="G423" t="s">
+      <c r="D424" t="s">
+        <v>6</v>
+      </c>
+      <c r="F424" t="s">
+        <v>16</v>
+      </c>
+      <c r="G424" t="s">
         <v>145</v>
       </c>
-      <c r="H423" t="s">
-        <v>220</v>
-      </c>
-      <c r="I423">
-        <v>5</v>
-      </c>
-      <c r="J423">
+      <c r="H424" t="s">
+        <v>221</v>
+      </c>
+      <c r="I424">
+        <v>5</v>
+      </c>
+      <c r="J424">
         <f t="shared" si="1"/>
         <v>1.3817000000000013</v>
       </c>
-      <c r="K423">
+      <c r="K424">
         <f>33.94*(1-99%)</f>
         <v>0.33940000000000026</v>
       </c>
-      <c r="L423">
+      <c r="L424">
         <f>48.48*(1-95%)</f>
         <v>2.4240000000000022</v>
       </c>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A424" t="s">
+    <row r="425" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A425" t="s">
         <v>84</v>
       </c>
-      <c r="B424">
+      <c r="B425">
         <f t="shared" si="0"/>
         <v>14.559999999999999</v>
       </c>
-      <c r="C424" t="s">
+      <c r="C425" t="s">
         <v>26</v>
       </c>
-      <c r="D424" t="s">
-        <v>6</v>
-      </c>
-      <c r="F424" t="s">
-        <v>16</v>
-      </c>
-      <c r="G424" t="s">
+      <c r="D425" t="s">
+        <v>6</v>
+      </c>
+      <c r="F425" t="s">
+        <v>16</v>
+      </c>
+      <c r="G425" t="s">
         <v>89</v>
       </c>
-      <c r="I424">
-        <v>5</v>
-      </c>
-      <c r="J424">
+      <c r="I425">
+        <v>5</v>
+      </c>
+      <c r="J425">
         <f t="shared" si="1"/>
         <v>14.559999999999999</v>
       </c>
-      <c r="K424">
+      <c r="K425">
         <v>11.99</v>
       </c>
-      <c r="L424">
+      <c r="L425">
         <v>17.13</v>
       </c>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A425" t="s">
+    <row r="426" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A426" t="s">
         <v>34</v>
       </c>
-      <c r="B425">
+      <c r="B426">
         <f t="shared" si="0"/>
         <v>0.34499999999999997</v>
       </c>
-      <c r="C425" t="s">
-        <v>8</v>
-      </c>
-      <c r="D425" t="s">
+      <c r="C426" t="s">
+        <v>8</v>
+      </c>
+      <c r="D426" t="s">
         <v>23</v>
       </c>
-      <c r="F425" t="s">
-        <v>16</v>
-      </c>
-      <c r="G425" t="s">
+      <c r="F426" t="s">
+        <v>16</v>
+      </c>
+      <c r="G426" t="s">
         <v>24</v>
       </c>
-      <c r="I425">
-        <v>5</v>
-      </c>
-      <c r="J425">
+      <c r="I426">
+        <v>5</v>
+      </c>
+      <c r="J426">
         <f t="shared" si="1"/>
         <v>0.34499999999999997</v>
       </c>
-      <c r="K425">
+      <c r="K426">
         <v>0.27</v>
       </c>
-      <c r="L425">
+      <c r="L426">
         <v>0.42</v>
       </c>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A426" t="s">
+    <row r="427" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A427" t="s">
         <v>83</v>
       </c>
-      <c r="B426">
+      <c r="B427">
         <f t="shared" si="0"/>
         <v>7.4749999999999996</v>
       </c>
-      <c r="C426" t="s">
+      <c r="C427" t="s">
         <v>131</v>
       </c>
-      <c r="D426" t="s">
+      <c r="D427" t="s">
         <v>22</v>
       </c>
-      <c r="F426" t="s">
-        <v>16</v>
-      </c>
-      <c r="G426" t="s">
+      <c r="F427" t="s">
+        <v>16</v>
+      </c>
+      <c r="G427" t="s">
         <v>88</v>
       </c>
-      <c r="I426">
-        <v>5</v>
-      </c>
-      <c r="J426">
+      <c r="I427">
+        <v>5</v>
+      </c>
+      <c r="J427">
         <f t="shared" si="1"/>
         <v>7.4749999999999996</v>
       </c>
-      <c r="K426">
+      <c r="K427">
         <v>2.35</v>
       </c>
-      <c r="L426">
+      <c r="L427">
         <v>12.6</v>
       </c>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A427" t="s">
+    <row r="428" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A428" t="s">
         <v>73</v>
       </c>
-      <c r="B427">
+      <c r="B428">
         <f t="shared" si="0"/>
         <v>-1.5</v>
       </c>
-      <c r="C427" t="s">
+      <c r="C428" t="s">
         <v>131</v>
       </c>
-      <c r="D427" t="s">
-        <v>6</v>
-      </c>
-      <c r="F427" t="s">
-        <v>16</v>
-      </c>
-      <c r="G427" t="s">
+      <c r="D428" t="s">
+        <v>6</v>
+      </c>
+      <c r="F428" t="s">
+        <v>16</v>
+      </c>
+      <c r="G428" t="s">
         <v>140</v>
       </c>
-      <c r="I427">
-        <v>5</v>
-      </c>
-      <c r="J427">
+      <c r="I428">
+        <v>5</v>
+      </c>
+      <c r="J428">
         <f t="shared" si="1"/>
         <v>-1.5</v>
       </c>
-      <c r="K427">
+      <c r="K428">
         <v>-2.63</v>
       </c>
-      <c r="L427">
+      <c r="L428">
         <v>-0.37</v>
       </c>
-      <c r="M427" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="428" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A428" s="2"/>
-      <c r="J428" s="2"/>
+      <c r="M428" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="429" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A429" s="1" t="s">
+      <c r="A429" s="2"/>
+      <c r="J429" s="2"/>
+    </row>
+    <row r="430" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A430" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B429" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A430" t="s">
-        <v>1</v>
-      </c>
-      <c r="B430">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="431" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="B430" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="431" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
+        <v>1</v>
+      </c>
+      <c r="B431">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A432" t="s">
         <v>2</v>
       </c>
-      <c r="B431" s="22" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A432" t="s">
-        <v>3</v>
-      </c>
-      <c r="B432" t="s">
-        <v>4</v>
+      <c r="B432" s="22" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="433" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B433" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="434" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B434" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="435" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B435" t="s">
-        <v>219</v>
+        <v>8</v>
       </c>
     </row>
     <row r="436" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
+        <v>9</v>
+      </c>
+      <c r="B436" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="437" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A437" t="s">
         <v>18</v>
       </c>
-      <c r="B436" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="437" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A437" s="1" t="s">
+      <c r="B437" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="438" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A438" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="438" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A438" s="5" t="s">
+    <row r="439" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A439" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B438" s="5" t="s">
+      <c r="B439" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C438" s="5" t="s">
+      <c r="C439" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D438" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E438" s="5" t="s">
+      <c r="D439" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E439" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F438" s="5" t="s">
+      <c r="F439" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G438" s="5" t="s">
+      <c r="G439" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H438" s="5" t="s">
+      <c r="H439" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I438" s="5" t="s">
+      <c r="I439" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="J438" s="5" t="s">
+      <c r="J439" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="K438" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="L438" s="5" t="s">
+      <c r="K439" s="5" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="439" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A439" t="str">
-        <f>B429</f>
+      <c r="L439" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="440" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A440" t="str">
+        <f>B430</f>
         <v>silica gel production, for sorbent-based direct air capture system</v>
       </c>
-      <c r="B439">
-        <v>1</v>
-      </c>
-      <c r="C439" t="s">
-        <v>8</v>
-      </c>
-      <c r="D439" t="s">
-        <v>6</v>
-      </c>
-      <c r="F439" t="s">
+      <c r="B440">
+        <v>1</v>
+      </c>
+      <c r="C440" t="s">
+        <v>8</v>
+      </c>
+      <c r="D440" t="s">
+        <v>6</v>
+      </c>
+      <c r="F440" t="s">
         <v>15</v>
       </c>
-      <c r="G439" s="7" t="str">
-        <f>B431</f>
+      <c r="G440" s="7" t="str">
+        <f>B432</f>
         <v>silica gel</v>
       </c>
-    </row>
-    <row r="440" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A440" t="s">
-        <v>81</v>
-      </c>
-      <c r="B440">
-        <v>3.9</v>
-      </c>
-      <c r="C440" t="s">
-        <v>26</v>
-      </c>
-      <c r="D440" t="s">
-        <v>6</v>
-      </c>
-      <c r="F440" t="s">
-        <v>16</v>
-      </c>
-      <c r="G440" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q440" s="4"/>
-      <c r="S440" s="4"/>
     </row>
     <row r="441" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B441">
-        <v>0.66</v>
+        <v>3.9</v>
       </c>
       <c r="C441" t="s">
         <v>26</v>
@@ -9558,272 +9550,271 @@
         <v>16</v>
       </c>
       <c r="G441" t="s">
-        <v>87</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="Q441" s="4"/>
+      <c r="S441" s="4"/>
     </row>
     <row r="442" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B442">
-        <v>19.5</v>
+        <v>0.66</v>
       </c>
       <c r="C442" t="s">
         <v>26</v>
       </c>
       <c r="D442" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F442" t="s">
         <v>16</v>
       </c>
       <c r="G442" t="s">
-        <v>88</v>
-      </c>
-      <c r="I442">
-        <v>5</v>
-      </c>
-      <c r="J442">
-        <f>B442</f>
-        <v>19.5</v>
-      </c>
-      <c r="K442">
-        <v>15</v>
-      </c>
-      <c r="L442">
-        <v>24</v>
+        <v>87</v>
       </c>
     </row>
     <row r="443" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B443">
-        <v>40</v>
+        <v>19.5</v>
       </c>
       <c r="C443" t="s">
         <v>26</v>
       </c>
       <c r="D443" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F443" t="s">
         <v>16</v>
       </c>
       <c r="G443" t="s">
+        <v>88</v>
+      </c>
+      <c r="I443">
+        <v>5</v>
+      </c>
+      <c r="J443">
+        <f>B443</f>
+        <v>19.5</v>
+      </c>
+      <c r="K443">
+        <v>15</v>
+      </c>
+      <c r="L443">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="444" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A444" t="s">
+        <v>84</v>
+      </c>
+      <c r="B444">
+        <v>40</v>
+      </c>
+      <c r="C444" t="s">
+        <v>26</v>
+      </c>
+      <c r="D444" t="s">
+        <v>6</v>
+      </c>
+      <c r="F444" t="s">
+        <v>16</v>
+      </c>
+      <c r="G444" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="444" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A444" t="s">
+    <row r="445" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A445" t="s">
         <v>195</v>
       </c>
-      <c r="B444">
+      <c r="B445">
         <f>-35/1000</f>
         <v>-3.5000000000000003E-2</v>
       </c>
-      <c r="C444" t="s">
+      <c r="C445" t="s">
         <v>26</v>
       </c>
-      <c r="D444" t="s">
+      <c r="D445" t="s">
         <v>49</v>
       </c>
-      <c r="F444" t="s">
-        <v>16</v>
-      </c>
-      <c r="G444" t="s">
+      <c r="F445" t="s">
+        <v>16</v>
+      </c>
+      <c r="G445" t="s">
         <v>149</v>
       </c>
-      <c r="M444" s="2"/>
-    </row>
-    <row r="445" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A445" t="s">
+      <c r="M445" s="2"/>
+    </row>
+    <row r="446" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A446" t="s">
         <v>148</v>
       </c>
-      <c r="B445" s="6">
+      <c r="B446" s="6">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="D445" t="s">
-        <v>6</v>
-      </c>
-      <c r="E445" t="s">
+      <c r="D446" t="s">
+        <v>6</v>
+      </c>
+      <c r="E446" t="s">
         <v>85</v>
       </c>
-      <c r="F445" t="s">
+      <c r="F446" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="446" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A446" s="2"/>
-      <c r="J446" s="2"/>
-    </row>
     <row r="447" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A447" s="1" t="s">
+      <c r="A447" s="2"/>
+      <c r="J447" s="2"/>
+    </row>
+    <row r="448" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A448" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B447" s="1" t="s">
+      <c r="B448" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="448" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A448" t="s">
-        <v>1</v>
-      </c>
-      <c r="B448">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="449" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
+        <v>1</v>
+      </c>
+      <c r="B449">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="450" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A450" t="s">
         <v>2</v>
       </c>
-      <c r="B449" s="8" t="s">
+      <c r="B450" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A450" t="s">
+    <row r="451" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A451" t="s">
         <v>3</v>
       </c>
-      <c r="B450" t="s">
+      <c r="B451" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A451" t="s">
-        <v>5</v>
-      </c>
-      <c r="B451" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
+        <v>5</v>
+      </c>
+      <c r="B452" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="453" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A453" t="s">
         <v>7</v>
       </c>
-      <c r="B452" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A453" t="s">
+      <c r="B453" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="454" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A454" t="s">
         <v>9</v>
       </c>
-      <c r="B453" t="s">
+      <c r="B454" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A454" t="s">
+    <row r="455" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A455" t="s">
         <v>18</v>
       </c>
-      <c r="B454" t="s">
+      <c r="B455" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="455" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A455" s="1" t="s">
+    <row r="456" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A456" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A456" t="s">
+    <row r="457" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A457" t="s">
         <v>11</v>
       </c>
-      <c r="B456" t="s">
+      <c r="B457" t="s">
         <v>12</v>
       </c>
-      <c r="C456" t="s">
+      <c r="C457" t="s">
         <v>7</v>
       </c>
-      <c r="D456" t="s">
-        <v>5</v>
-      </c>
-      <c r="E456" t="s">
+      <c r="D457" t="s">
+        <v>5</v>
+      </c>
+      <c r="E457" t="s">
         <v>13</v>
       </c>
-      <c r="F456" t="s">
+      <c r="F457" t="s">
         <v>3</v>
       </c>
-      <c r="G456" t="s">
+      <c r="G457" t="s">
         <v>2</v>
       </c>
-      <c r="H456" t="s">
+      <c r="H457" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="457" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A457" t="s">
+    <row r="458" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A458" t="s">
         <v>97</v>
       </c>
-      <c r="B457">
-        <v>1</v>
-      </c>
-      <c r="C457" t="s">
-        <v>8</v>
-      </c>
-      <c r="D457" t="s">
-        <v>6</v>
-      </c>
-      <c r="F457" t="s">
+      <c r="B458">
+        <v>1</v>
+      </c>
+      <c r="C458" t="s">
+        <v>8</v>
+      </c>
+      <c r="D458" t="s">
+        <v>6</v>
+      </c>
+      <c r="F458" t="s">
         <v>15</v>
       </c>
-      <c r="G457" s="8" t="s">
+      <c r="G458" s="8" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A458" t="s">
+    <row r="459" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A459" t="s">
         <v>194</v>
       </c>
-      <c r="B458">
+      <c r="B459">
         <v>9.9999999999999986E-10</v>
       </c>
-      <c r="C458" t="s">
+      <c r="C459" t="s">
         <v>21</v>
       </c>
-      <c r="D458" t="s">
+      <c r="D459" t="s">
         <v>49</v>
       </c>
-      <c r="F458" t="s">
-        <v>16</v>
-      </c>
-      <c r="G458" t="s">
+      <c r="F459" t="s">
+        <v>16</v>
+      </c>
+      <c r="G459" t="s">
         <v>196</v>
-      </c>
-      <c r="H458" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A459" t="s">
-        <v>152</v>
-      </c>
-      <c r="B459">
-        <v>1.0000000000000001E-7</v>
-      </c>
-      <c r="C459" t="s">
-        <v>17</v>
-      </c>
-      <c r="D459" t="s">
-        <v>6</v>
-      </c>
-      <c r="F459" t="s">
-        <v>16</v>
-      </c>
-      <c r="G459" t="s">
-        <v>153</v>
       </c>
       <c r="H459" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
-        <v>42</v>
+        <v>152</v>
       </c>
       <c r="B460">
-        <v>9.9999999999999995E-7</v>
+        <v>1.0000000000000001E-7</v>
       </c>
       <c r="C460" t="s">
         <v>17</v>
@@ -9835,18 +9826,18 @@
         <v>16</v>
       </c>
       <c r="G460" t="s">
-        <v>30</v>
+        <v>153</v>
       </c>
       <c r="H460" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="B461">
-        <v>2.9999999999999999E-7</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="C461" t="s">
         <v>17</v>
@@ -9858,108 +9849,108 @@
         <v>16</v>
       </c>
       <c r="G461" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
       <c r="H461" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="B462">
-        <v>3.1999999999999999E-5</v>
+        <v>2.9999999999999999E-7</v>
       </c>
       <c r="C462" t="s">
         <v>17</v>
       </c>
       <c r="D462" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F462" t="s">
         <v>16</v>
       </c>
       <c r="G462" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="H462" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="B463">
-        <v>9.9999999999999995E-7</v>
+        <v>3.1999999999999999E-5</v>
       </c>
       <c r="C463" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D463" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F463" t="s">
         <v>16</v>
       </c>
       <c r="G463" t="s">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="H463" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="464" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
+        <v>77</v>
+      </c>
+      <c r="B464">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="C464" t="s">
+        <v>8</v>
+      </c>
+      <c r="D464" t="s">
+        <v>23</v>
+      </c>
+      <c r="F464" t="s">
+        <v>16</v>
+      </c>
+      <c r="G464" t="s">
+        <v>78</v>
+      </c>
+      <c r="H464" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="465" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A465" t="s">
         <v>102</v>
       </c>
-      <c r="B464">
+      <c r="B465">
         <v>1.0400000000000001E-3</v>
       </c>
-      <c r="C464" t="s">
+      <c r="C465" t="s">
         <v>21</v>
       </c>
-      <c r="D464" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F464" t="s">
-        <v>16</v>
-      </c>
-      <c r="G464" t="s">
+      <c r="D465" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F465" t="s">
+        <v>16</v>
+      </c>
+      <c r="G465" t="s">
         <v>132</v>
-      </c>
-      <c r="H464" t="s">
-        <v>107</v>
-      </c>
-      <c r="J464" s="2"/>
-    </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A465" t="s">
-        <v>103</v>
-      </c>
-      <c r="B465">
-        <v>1.3000000000000002E-4</v>
-      </c>
-      <c r="C465" t="s">
-        <v>17</v>
-      </c>
-      <c r="D465" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F465" t="s">
-        <v>16</v>
-      </c>
-      <c r="G465" t="s">
-        <v>33</v>
       </c>
       <c r="H465" t="s">
         <v>107</v>
       </c>
+      <c r="J465" s="2"/>
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B466">
         <v>1.3000000000000002E-4</v>
@@ -9974,7 +9965,7 @@
         <v>16</v>
       </c>
       <c r="G466" t="s">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="H466" t="s">
         <v>107</v>
@@ -9982,10 +9973,10 @@
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B467">
-        <v>1.1999999999999999E-6</v>
+        <v>1.3000000000000002E-4</v>
       </c>
       <c r="C467" t="s">
         <v>17</v>
@@ -9997,7 +9988,7 @@
         <v>16</v>
       </c>
       <c r="G467" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H467" t="s">
         <v>107</v>
@@ -10005,10 +9996,10 @@
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B468">
-        <v>2.5000000000000002E-6</v>
+        <v>1.1999999999999999E-6</v>
       </c>
       <c r="C468" t="s">
         <v>17</v>
@@ -10020,7 +10011,7 @@
         <v>16</v>
       </c>
       <c r="G468" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H468" t="s">
         <v>107</v>
@@ -10028,22 +10019,22 @@
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="B469">
-        <v>1.8E-3</v>
+        <v>2.5000000000000002E-6</v>
       </c>
       <c r="C469" t="s">
         <v>17</v>
       </c>
       <c r="D469" s="10" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F469" t="s">
         <v>16</v>
       </c>
       <c r="G469" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="H469" t="s">
         <v>107</v>
@@ -10051,22 +10042,22 @@
     </row>
     <row r="470" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="B470">
-        <v>1.1999999999999999E-4</v>
+        <v>1.8E-3</v>
       </c>
       <c r="C470" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D470" s="10" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F470" t="s">
         <v>16</v>
       </c>
       <c r="G470" t="s">
-        <v>36</v>
+        <v>147</v>
       </c>
       <c r="H470" t="s">
         <v>107</v>
@@ -10074,59 +10065,59 @@
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
-        <v>106</v>
-      </c>
-      <c r="B471" s="6">
-        <v>8.2000000000000001E-11</v>
+        <v>35</v>
+      </c>
+      <c r="B471">
+        <v>1.1999999999999999E-4</v>
       </c>
       <c r="C471" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D471" s="10" t="s">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="F471" t="s">
         <v>16</v>
       </c>
       <c r="G471" t="s">
-        <v>133</v>
+        <v>36</v>
       </c>
       <c r="H471" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>102</v>
-      </c>
-      <c r="B472">
-        <v>3.3E-3</v>
+        <v>106</v>
+      </c>
+      <c r="B472" s="6">
+        <v>8.2000000000000001E-11</v>
       </c>
       <c r="C472" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D472" s="10" t="s">
-        <v>6</v>
+        <v>139</v>
       </c>
       <c r="F472" t="s">
         <v>16</v>
       </c>
       <c r="G472" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H472" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="473" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>59</v>
-      </c>
-      <c r="B473" s="2">
-        <v>1.7E-5</v>
+        <v>102</v>
+      </c>
+      <c r="B473">
+        <v>3.3E-3</v>
       </c>
       <c r="C473" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D473" s="10" t="s">
         <v>6</v>
@@ -10135,18 +10126,18 @@
         <v>16</v>
       </c>
       <c r="G473" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H473" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>42</v>
-      </c>
-      <c r="B474">
-        <v>3.6999999999999998E-5</v>
+        <v>59</v>
+      </c>
+      <c r="B474" s="2">
+        <v>1.7E-5</v>
       </c>
       <c r="C474" t="s">
         <v>17</v>
@@ -10158,7 +10149,7 @@
         <v>16</v>
       </c>
       <c r="G474" t="s">
-        <v>30</v>
+        <v>128</v>
       </c>
       <c r="H474" t="s">
         <v>108</v>
@@ -10166,22 +10157,22 @@
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>194</v>
+        <v>42</v>
       </c>
       <c r="B475">
-        <v>4.8E-8</v>
+        <v>3.6999999999999998E-5</v>
       </c>
       <c r="C475" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D475" s="10" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="F475" t="s">
         <v>16</v>
       </c>
       <c r="G475" t="s">
-        <v>196</v>
+        <v>30</v>
       </c>
       <c r="H475" t="s">
         <v>108</v>
@@ -10189,22 +10180,22 @@
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="B476">
-        <v>1.9E-6</v>
+        <v>4.8E-8</v>
       </c>
       <c r="C476" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D476" s="10" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="F476" t="s">
         <v>16</v>
       </c>
       <c r="G476" t="s">
-        <v>153</v>
+        <v>196</v>
       </c>
       <c r="H476" t="s">
         <v>108</v>
@@ -10212,22 +10203,22 @@
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>35</v>
+        <v>152</v>
       </c>
       <c r="B477">
-        <v>3.4000000000000002E-4</v>
+        <v>1.9E-6</v>
       </c>
       <c r="C477" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D477" s="10" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="F477" t="s">
         <v>16</v>
       </c>
       <c r="G477" t="s">
-        <v>36</v>
+        <v>153</v>
       </c>
       <c r="H477" t="s">
         <v>108</v>
@@ -10235,83 +10226,82 @@
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="B478">
-        <v>0.11799999999999999</v>
+        <v>3.4000000000000002E-4</v>
       </c>
       <c r="C478" t="s">
         <v>8</v>
       </c>
       <c r="D478" s="10" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F478" t="s">
         <v>16</v>
       </c>
       <c r="G478" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="H478" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
+        <v>77</v>
+      </c>
+      <c r="B479">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="C479" t="s">
+        <v>8</v>
+      </c>
+      <c r="D479" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F479" t="s">
+        <v>16</v>
+      </c>
+      <c r="G479" t="s">
+        <v>78</v>
+      </c>
+      <c r="H479" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="480" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A480" t="s">
         <v>65</v>
       </c>
-      <c r="B479">
+      <c r="B480">
         <v>-4.4000000000000003E-3</v>
       </c>
-      <c r="C479" t="s">
+      <c r="C480" t="s">
         <v>131</v>
       </c>
-      <c r="D479" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F479" t="s">
-        <v>16</v>
-      </c>
-      <c r="G479" t="s">
+      <c r="D480" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F480" t="s">
+        <v>16</v>
+      </c>
+      <c r="G480" t="s">
         <v>161</v>
-      </c>
-      <c r="H479" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="480" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A480" t="s">
-        <v>66</v>
-      </c>
-      <c r="B480">
-        <v>-2.5999999999999998E-4</v>
-      </c>
-      <c r="C480" t="s">
-        <v>21</v>
-      </c>
-      <c r="D480" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F480" t="s">
-        <v>16</v>
-      </c>
-      <c r="G480" t="s">
-        <v>160</v>
       </c>
       <c r="H480" t="s">
         <v>76</v>
       </c>
-      <c r="J480" s="2"/>
-    </row>
-    <row r="481" spans="1:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="481" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="B481">
-        <v>-1.9999999999999999E-6</v>
+        <v>-2.5999999999999998E-4</v>
       </c>
       <c r="C481" t="s">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="D481" s="10" t="s">
         <v>6</v>
@@ -10320,21 +10310,22 @@
         <v>16</v>
       </c>
       <c r="G481" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="H481" t="s">
         <v>76</v>
       </c>
+      <c r="J481" s="2"/>
     </row>
     <row r="482" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B482">
-        <v>-2.7999999999999999E-6</v>
+        <v>-1.9999999999999999E-6</v>
       </c>
       <c r="C482" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="D482" s="10" t="s">
         <v>6</v>
@@ -10343,7 +10334,7 @@
         <v>16</v>
       </c>
       <c r="G482" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="H482" t="s">
         <v>76</v>
@@ -10351,13 +10342,13 @@
     </row>
     <row r="483" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B483">
-        <v>-1.1999999999999999E-6</v>
+        <v>-2.7999999999999999E-6</v>
       </c>
       <c r="C483" t="s">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="D483" s="10" t="s">
         <v>6</v>
@@ -10366,32 +10357,41 @@
         <v>16</v>
       </c>
       <c r="G483" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H483" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="485" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A485" s="14" t="s">
+    <row r="484" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A484" t="s">
+        <v>112</v>
+      </c>
+      <c r="B484">
+        <v>-1.1999999999999999E-6</v>
+      </c>
+      <c r="C484" t="s">
+        <v>131</v>
+      </c>
+      <c r="D484" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F484" t="s">
+        <v>16</v>
+      </c>
+      <c r="G484" t="s">
+        <v>137</v>
+      </c>
+      <c r="H484" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="486" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A486" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B485" s="14" t="s">
-        <v>301</v>
-      </c>
-      <c r="K485" s="16"/>
-      <c r="L485" s="16"/>
-      <c r="M485" s="16"/>
-      <c r="N485" s="16"/>
-      <c r="O485" s="16"/>
-      <c r="P485" s="16"/>
-    </row>
-    <row r="486" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A486" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B486" s="15" t="s">
-        <v>8</v>
+      <c r="B486" s="14" t="s">
+        <v>302</v>
       </c>
       <c r="K486" s="16"/>
       <c r="L486" s="16"/>
@@ -10402,10 +10402,10 @@
     </row>
     <row r="487" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A487" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="B487" s="15">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="B487" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="K487" s="16"/>
       <c r="L487" s="16"/>
@@ -10416,10 +10416,10 @@
     </row>
     <row r="488" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A488" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="B488" s="15" t="s">
-        <v>294</v>
+        <v>1</v>
+      </c>
+      <c r="B488" s="15">
+        <v>1</v>
       </c>
       <c r="K488" s="16"/>
       <c r="L488" s="16"/>
@@ -10430,10 +10430,10 @@
     </row>
     <row r="489" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A489" s="15" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B489" s="15" t="s">
-        <v>4</v>
+        <v>295</v>
       </c>
       <c r="K489" s="16"/>
       <c r="L489" s="16"/>
@@ -10444,10 +10444,10 @@
     </row>
     <row r="490" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A490" s="15" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B490" s="15" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K490" s="16"/>
       <c r="L490" s="16"/>
@@ -10458,10 +10458,10 @@
     </row>
     <row r="491" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A491" s="15" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B491" s="15" t="s">
-        <v>198</v>
+        <v>6</v>
       </c>
       <c r="K491" s="16"/>
       <c r="L491" s="16"/>
@@ -10472,10 +10472,10 @@
     </row>
     <row r="492" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A492" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="B492" s="17">
-        <v>0.61363636363636365</v>
+        <v>9</v>
+      </c>
+      <c r="B492" s="15" t="s">
+        <v>199</v>
       </c>
       <c r="K492" s="16"/>
       <c r="L492" s="16"/>
@@ -10485,8 +10485,11 @@
       <c r="P492" s="16"/>
     </row>
     <row r="493" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A493" s="14" t="s">
-        <v>10</v>
+      <c r="A493" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="B493" s="17">
+        <v>0.61363636363636365</v>
       </c>
       <c r="K493" s="16"/>
       <c r="L493" s="16"/>
@@ -10497,151 +10500,112 @@
     </row>
     <row r="494" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A494" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="K494" s="16"/>
+      <c r="L494" s="16"/>
+      <c r="M494" s="16"/>
+      <c r="N494" s="16"/>
+      <c r="O494" s="16"/>
+      <c r="P494" s="16"/>
+    </row>
+    <row r="495" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A495" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B494" s="14" t="s">
+      <c r="B495" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C494" s="14" t="s">
+      <c r="C495" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D494" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E494" s="14" t="s">
+      <c r="D495" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E495" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F494" s="14" t="s">
+      <c r="F495" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="G494" s="14" t="s">
+      <c r="G495" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H494" s="14" t="s">
+      <c r="H495" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I494" s="14" t="s">
+      <c r="I495" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="J494" s="1" t="s">
+      <c r="J495" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="K494" s="18" t="s">
+      <c r="K495" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="L494" s="18" t="s">
+      <c r="L495" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="M494" s="18" t="s">
+      <c r="M495" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="N494" s="18" t="s">
+      <c r="N495" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="O494" s="18" t="s">
+      <c r="O495" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="P494" s="18" t="s">
+      <c r="P495" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="Q494" s="1" t="s">
+      <c r="Q495" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="R494" s="1" t="s">
+      <c r="R495" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="S494" s="14" t="s">
+      <c r="S495" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="T494" s="1"/>
-    </row>
-    <row r="495" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A495" s="15" t="s">
-        <v>301</v>
-      </c>
-      <c r="B495" s="15">
-        <v>1</v>
-      </c>
-      <c r="C495" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D495" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F495" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G495" s="15" t="str">
-        <f>B488</f>
-        <v>carbon dioxide, captured</v>
-      </c>
-      <c r="H495" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="K495" s="16"/>
-      <c r="L495" s="16"/>
-      <c r="M495" s="16"/>
-      <c r="N495" s="16"/>
-      <c r="O495" s="16"/>
-      <c r="P495" s="16"/>
-      <c r="T495"/>
+      <c r="T495" s="1"/>
     </row>
     <row r="496" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A496" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="B496" s="19">
-        <v>6.7613636363636362E-2</v>
+        <v>302</v>
+      </c>
+      <c r="B496" s="15">
+        <v>1</v>
+      </c>
+      <c r="C496" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="D496" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E496" s="15" t="s">
-        <v>85</v>
-      </c>
       <c r="F496" s="15" t="s">
-        <v>20</v>
+        <v>15</v>
+      </c>
+      <c r="G496" s="15" t="str">
+        <f>B489</f>
+        <v>carbon dioxide, captured</v>
       </c>
       <c r="H496" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="I496" s="15">
-        <v>2</v>
-      </c>
-      <c r="J496">
-        <v>-2.6939455949206681</v>
-      </c>
-      <c r="K496" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="L496" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="M496" s="4">
-        <v>1</v>
-      </c>
-      <c r="N496" s="4">
-        <v>1.01</v>
-      </c>
-      <c r="O496" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="P496" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="Q496" s="4">
-        <v>1.05</v>
-      </c>
-      <c r="R496">
-        <v>0.16679850853156178</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="K496" s="16"/>
+      <c r="L496" s="16"/>
+      <c r="M496" s="16"/>
+      <c r="N496" s="16"/>
+      <c r="O496" s="16"/>
+      <c r="P496" s="16"/>
+      <c r="T496"/>
     </row>
     <row r="497" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A497" s="15" t="s">
-        <v>38</v>
+        <v>184</v>
       </c>
       <c r="B497" s="19">
-        <v>0.10738636363636363</v>
+        <v>6.7613636363636362E-2</v>
       </c>
       <c r="D497" s="15" t="s">
         <v>6</v>
@@ -10659,7 +10623,7 @@
         <v>2</v>
       </c>
       <c r="J497">
-        <v>-2.2313220729725551</v>
+        <v>-2.6939455949206681</v>
       </c>
       <c r="K497" s="4">
         <v>1.1000000000000001</v>
@@ -10688,10 +10652,10 @@
     </row>
     <row r="498" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A498" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="B498" s="20">
-        <v>1E-4</v>
+        <v>38</v>
+      </c>
+      <c r="B498" s="19">
+        <v>0.10738636363636363</v>
       </c>
       <c r="D498" s="15" t="s">
         <v>6</v>
@@ -10702,11 +10666,14 @@
       <c r="F498" s="15" t="s">
         <v>20</v>
       </c>
+      <c r="H498" s="15" t="s">
+        <v>185</v>
+      </c>
       <c r="I498" s="15">
         <v>2</v>
       </c>
       <c r="J498">
-        <v>-9.2103403719761818</v>
+        <v>-2.2313220729725551</v>
       </c>
       <c r="K498" s="4">
         <v>1.1000000000000001</v>
@@ -10727,36 +10694,33 @@
         <v>1.2</v>
       </c>
       <c r="Q498" s="4">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="R498">
-        <v>0.26139455023340635</v>
+        <v>0.16679850853156178</v>
       </c>
     </row>
     <row r="499" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A499" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B499" s="15">
-        <v>9.6600000000000002E-3</v>
-      </c>
-      <c r="C499" s="15" t="s">
-        <v>131</v>
+        <v>186</v>
+      </c>
+      <c r="B499" s="20">
+        <v>1E-4</v>
       </c>
       <c r="D499" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="E499" s="15" t="s">
+        <v>85</v>
+      </c>
       <c r="F499" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G499" s="15" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="I499" s="15">
         <v>2</v>
       </c>
       <c r="J499">
-        <v>-4.6397616307577101</v>
+        <v>-9.2103403719761818</v>
       </c>
       <c r="K499" s="4">
         <v>1.1000000000000001</v>
@@ -10776,37 +10740,37 @@
       <c r="P499" s="4">
         <v>1.2</v>
       </c>
-      <c r="Q499">
-        <v>1.05</v>
+      <c r="Q499" s="4">
+        <v>1.5</v>
       </c>
       <c r="R499">
-        <v>0.16679850853156178</v>
+        <v>0.26139455023340635</v>
       </c>
     </row>
     <row r="500" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A500" s="15" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B500" s="15">
-        <v>0.1</v>
+        <v>9.6600000000000002E-3</v>
       </c>
       <c r="C500" s="15" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="D500" s="15" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F500" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G500" s="15" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I500" s="15">
         <v>2</v>
       </c>
       <c r="J500">
-        <v>-2.3025850929940455</v>
+        <v>-4.6397616307577101</v>
       </c>
       <c r="K500" s="4">
         <v>1.1000000000000001</v>
@@ -10835,82 +10799,82 @@
     </row>
     <row r="501" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A501" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B501" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="C501" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D501" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F501" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G501" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I501" s="15">
+        <v>2</v>
+      </c>
+      <c r="J501">
+        <v>-2.3025850929940455</v>
+      </c>
+      <c r="K501" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L501" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="M501" s="4">
+        <v>1</v>
+      </c>
+      <c r="N501" s="4">
+        <v>1.01</v>
+      </c>
+      <c r="O501" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="P501" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="Q501">
+        <v>1.05</v>
+      </c>
+      <c r="R501">
+        <v>0.16679850853156178</v>
+      </c>
+    </row>
+    <row r="502" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A502" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="B501" s="15">
+      <c r="B502" s="15">
         <f>0.4+((3.7-0.4)*0.4)</f>
         <v>1.7200000000000002</v>
       </c>
-      <c r="C501" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D501" s="15" t="s">
+      <c r="C502" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D502" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F501" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G501" s="15" t="s">
+      <c r="F502" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G502" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="H501" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="I501" s="15">
-        <v>2</v>
-      </c>
-      <c r="J501">
-        <v>0.40546510810816438</v>
-      </c>
-      <c r="K501" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="L501" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="M501" s="4">
-        <v>1</v>
-      </c>
-      <c r="N501" s="4">
-        <v>1.01</v>
-      </c>
-      <c r="O501" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="P501" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="Q501">
-        <v>1.05</v>
-      </c>
-      <c r="R501">
-        <v>0.16679850853156178</v>
-      </c>
-    </row>
-    <row r="502" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A502" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B502" s="39">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="C502" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D502" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F502" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G502" s="15" t="s">
-        <v>141</v>
+      <c r="H502" s="15" t="s">
+        <v>198</v>
       </c>
       <c r="I502" s="15">
         <v>2</v>
       </c>
       <c r="J502">
-        <v>-5.521460917862246</v>
+        <v>0.40546510810816438</v>
       </c>
       <c r="K502" s="4">
         <v>1.1000000000000001</v>
@@ -10939,10 +10903,10 @@
     </row>
     <row r="503" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A503" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="B503" s="15">
-        <v>1E-4</v>
+        <v>90</v>
+      </c>
+      <c r="B503" s="39">
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="C503" s="15" t="s">
         <v>17</v>
@@ -10954,13 +10918,13 @@
         <v>16</v>
       </c>
       <c r="G503" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I503" s="15">
         <v>2</v>
       </c>
       <c r="J503">
-        <v>-9.2103403719761818</v>
+        <v>-5.521460917862246</v>
       </c>
       <c r="K503" s="4">
         <v>1.1000000000000001</v>
@@ -10989,7 +10953,7 @@
     </row>
     <row r="504" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A504" s="15" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="B504" s="15">
         <v>1E-4</v>
@@ -11004,7 +10968,7 @@
         <v>16</v>
       </c>
       <c r="G504" s="15" t="s">
-        <v>190</v>
+        <v>142</v>
       </c>
       <c r="I504" s="15">
         <v>2</v>
@@ -11038,236 +11002,235 @@
       </c>
     </row>
     <row r="505" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="K505" s="16"/>
-      <c r="L505" s="16"/>
-      <c r="M505" s="16"/>
-      <c r="N505" s="16"/>
-      <c r="O505" s="16"/>
-      <c r="P505" s="16"/>
-    </row>
-    <row r="506" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A506" s="1" t="s">
+      <c r="A505" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="B505" s="15">
+        <v>1E-4</v>
+      </c>
+      <c r="C505" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D505" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F505" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G505" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="I505" s="15">
+        <v>2</v>
+      </c>
+      <c r="J505">
+        <v>-9.2103403719761818</v>
+      </c>
+      <c r="K505" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L505" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="M505" s="4">
+        <v>1</v>
+      </c>
+      <c r="N505" s="4">
+        <v>1.01</v>
+      </c>
+      <c r="O505" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="P505" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="Q505">
+        <v>1.05</v>
+      </c>
+      <c r="R505">
+        <v>0.16679850853156178</v>
+      </c>
+    </row>
+    <row r="506" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="K506" s="16"/>
+      <c r="L506" s="16"/>
+      <c r="M506" s="16"/>
+      <c r="N506" s="16"/>
+      <c r="O506" s="16"/>
+      <c r="P506" s="16"/>
+    </row>
+    <row r="507" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A507" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B506" s="5" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="507" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A507" t="s">
+      <c r="B507" s="5" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="508" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A508" t="s">
         <v>7</v>
       </c>
-      <c r="B507" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="508" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A508" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B508">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="509" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A509" t="s">
-        <v>2</v>
-      </c>
-      <c r="B509" t="s">
-        <v>294</v>
+      <c r="B508" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="509" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A509" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B509">
+        <v>1</v>
       </c>
     </row>
     <row r="510" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B510" t="s">
-        <v>4</v>
+        <v>295</v>
       </c>
     </row>
     <row r="511" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B511" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="512" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B512" t="s">
-        <v>191</v>
+        <v>6</v>
       </c>
     </row>
     <row r="513" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B513" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="514" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
-        <v>171</v>
-      </c>
-      <c r="B514">
-        <v>0.06</v>
+        <v>9</v>
+      </c>
+      <c r="B514" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="515" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="B515">
-        <v>1</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="516" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
+        <v>192</v>
+      </c>
+      <c r="B516">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="517" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A517" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="517" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A517" s="1" t="s">
+    <row r="518" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A518" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B517" s="1" t="s">
+      <c r="B518" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C517" s="5" t="s">
+      <c r="C518" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D517" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E517" s="5" t="s">
+      <c r="D518" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E518" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F517" s="5" t="s">
+      <c r="F518" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G517" s="5" t="s">
+      <c r="G518" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H517" s="5" t="s">
+      <c r="H518" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I517" s="5" t="s">
+      <c r="I518" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="J517" s="5" t="s">
+      <c r="J518" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="K517" s="5" t="s">
+      <c r="K518" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="L517" s="5" t="s">
+      <c r="L518" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="M517" s="5" t="s">
+      <c r="M518" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="N517" s="5" t="s">
+      <c r="N518" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="O517" s="5" t="s">
+      <c r="O518" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="P517" s="5" t="s">
+      <c r="P518" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="Q517" s="5" t="s">
+      <c r="Q518" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="R517" s="5" t="s">
+      <c r="R518" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="S517" s="5" t="s">
+      <c r="S518" s="5" t="s">
         <v>182</v>
-      </c>
-    </row>
-    <row r="518" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A518" t="s">
-        <v>302</v>
-      </c>
-      <c r="B518">
-        <v>1</v>
-      </c>
-      <c r="C518" t="s">
-        <v>8</v>
-      </c>
-      <c r="D518" t="s">
-        <v>6</v>
-      </c>
-      <c r="F518" t="s">
-        <v>15</v>
-      </c>
-      <c r="G518" t="str">
-        <f>B509</f>
-        <v>carbon dioxide, captured</v>
       </c>
     </row>
     <row r="519" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
-        <v>184</v>
+        <v>303</v>
       </c>
       <c r="B519">
-        <f>0.11*(1-B514)</f>
-        <v>0.10339999999999999</v>
+        <v>1</v>
+      </c>
+      <c r="C519" t="s">
+        <v>8</v>
       </c>
       <c r="D519" t="s">
         <v>6</v>
       </c>
-      <c r="E519" t="s">
-        <v>85</v>
-      </c>
       <c r="F519" t="s">
-        <v>20</v>
-      </c>
-      <c r="H519" t="s">
-        <v>193</v>
-      </c>
-      <c r="I519">
-        <v>2</v>
-      </c>
-      <c r="J519">
-        <v>-2.2678230385440798</v>
-      </c>
-      <c r="K519">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="L519">
-        <v>1.2</v>
-      </c>
-      <c r="M519">
-        <v>1</v>
-      </c>
-      <c r="N519">
-        <v>1.01</v>
-      </c>
-      <c r="O519">
-        <v>1.2</v>
-      </c>
-      <c r="P519">
-        <v>1.2</v>
-      </c>
-      <c r="Q519">
-        <v>1.05</v>
-      </c>
-      <c r="R519">
-        <v>0.16679850853156178</v>
+        <v>15</v>
+      </c>
+      <c r="G519" t="str">
+        <f>B510</f>
+        <v>carbon dioxide, captured</v>
       </c>
     </row>
     <row r="520" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>38</v>
+        <v>184</v>
       </c>
       <c r="B520">
-        <f>0.11-B519</f>
-        <v>6.6000000000000086E-3</v>
+        <f>0.11*(1-B515)</f>
+        <v>0.10339999999999999</v>
       </c>
       <c r="D520" t="s">
         <v>6</v>
@@ -11285,7 +11248,7 @@
         <v>2</v>
       </c>
       <c r="J520">
-        <v>-5.0417129971418326</v>
+        <v>-2.2678230385440798</v>
       </c>
       <c r="K520">
         <v>1.1000000000000001</v>
@@ -11314,28 +11277,29 @@
     </row>
     <row r="521" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B521">
-        <v>9.6600000000000002E-3</v>
-      </c>
-      <c r="C521" t="s">
-        <v>131</v>
+        <f>0.11-B520</f>
+        <v>6.6000000000000086E-3</v>
       </c>
       <c r="D521" t="s">
         <v>6</v>
       </c>
+      <c r="E521" t="s">
+        <v>85</v>
+      </c>
       <c r="F521" t="s">
-        <v>16</v>
-      </c>
-      <c r="G521" t="s">
-        <v>32</v>
+        <v>20</v>
+      </c>
+      <c r="H521" t="s">
+        <v>193</v>
       </c>
       <c r="I521">
         <v>2</v>
       </c>
       <c r="J521">
-        <v>-4.6397616307577101</v>
+        <v>-5.0417129971418326</v>
       </c>
       <c r="K521">
         <v>1.1000000000000001</v>
@@ -11364,28 +11328,28 @@
     </row>
     <row r="522" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B522">
-        <v>6.9000000000000008E-3</v>
+        <v>9.6600000000000002E-3</v>
       </c>
       <c r="C522" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="D522" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F522" t="s">
         <v>16</v>
       </c>
       <c r="G522" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I522">
         <v>2</v>
       </c>
       <c r="J522">
-        <v>-4.976233867378923</v>
+        <v>-4.6397616307577101</v>
       </c>
       <c r="K522">
         <v>1.1000000000000001</v>
@@ -11414,79 +11378,79 @@
     </row>
     <row r="523" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
+        <v>34</v>
+      </c>
+      <c r="B523">
+        <v>6.9000000000000008E-3</v>
+      </c>
+      <c r="C523" t="s">
+        <v>8</v>
+      </c>
+      <c r="D523" t="s">
+        <v>23</v>
+      </c>
+      <c r="F523" t="s">
+        <v>16</v>
+      </c>
+      <c r="G523" t="s">
+        <v>24</v>
+      </c>
+      <c r="I523">
+        <v>2</v>
+      </c>
+      <c r="J523">
+        <v>-4.976233867378923</v>
+      </c>
+      <c r="K523">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L523">
+        <v>1.2</v>
+      </c>
+      <c r="M523">
+        <v>1</v>
+      </c>
+      <c r="N523">
+        <v>1.01</v>
+      </c>
+      <c r="O523">
+        <v>1.2</v>
+      </c>
+      <c r="P523">
+        <v>1.2</v>
+      </c>
+      <c r="Q523">
+        <v>1.05</v>
+      </c>
+      <c r="R523">
+        <v>0.16679850853156178</v>
+      </c>
+    </row>
+    <row r="524" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A524" t="s">
         <v>187</v>
       </c>
-      <c r="B523">
+      <c r="B524">
         <f>3.66*0.7</f>
         <v>2.5619999999999998</v>
       </c>
-      <c r="C523" t="s">
-        <v>8</v>
-      </c>
-      <c r="D523" t="s">
+      <c r="C524" t="s">
+        <v>8</v>
+      </c>
+      <c r="D524" t="s">
         <v>22</v>
       </c>
-      <c r="F523" t="s">
-        <v>16</v>
-      </c>
-      <c r="G523" t="s">
+      <c r="F524" t="s">
+        <v>16</v>
+      </c>
+      <c r="G524" t="s">
         <v>188</v>
-      </c>
-      <c r="I523">
-        <v>2</v>
-      </c>
-      <c r="J523">
-        <v>0.99635805462935334</v>
-      </c>
-      <c r="K523">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="L523">
-        <v>1.2</v>
-      </c>
-      <c r="M523">
-        <v>1</v>
-      </c>
-      <c r="N523">
-        <v>1.01</v>
-      </c>
-      <c r="O523">
-        <v>1.2</v>
-      </c>
-      <c r="P523">
-        <v>1.2</v>
-      </c>
-      <c r="Q523">
-        <v>1.05</v>
-      </c>
-      <c r="R523">
-        <v>0.16679850853156178</v>
-      </c>
-    </row>
-    <row r="524" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A524" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="B524" s="38">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="C524" t="s">
-        <v>17</v>
-      </c>
-      <c r="D524" t="s">
-        <v>6</v>
-      </c>
-      <c r="F524" t="s">
-        <v>16</v>
-      </c>
-      <c r="G524" t="s">
-        <v>141</v>
       </c>
       <c r="I524">
         <v>2</v>
       </c>
       <c r="J524">
-        <v>-6.9077552789821368</v>
+        <v>0.99635805462935334</v>
       </c>
       <c r="K524">
         <v>1.1000000000000001</v>
@@ -11513,252 +11477,277 @@
         <v>0.16679850853156178</v>
       </c>
     </row>
-    <row r="526" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A526" s="1" t="s">
+    <row r="525" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A525" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B525" s="38">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="C525" t="s">
+        <v>17</v>
+      </c>
+      <c r="D525" t="s">
+        <v>6</v>
+      </c>
+      <c r="F525" t="s">
+        <v>16</v>
+      </c>
+      <c r="G525" t="s">
+        <v>141</v>
+      </c>
+      <c r="I525">
+        <v>2</v>
+      </c>
+      <c r="J525">
+        <v>-6.9077552789821368</v>
+      </c>
+      <c r="K525">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L525">
+        <v>1.2</v>
+      </c>
+      <c r="M525">
+        <v>1</v>
+      </c>
+      <c r="N525">
+        <v>1.01</v>
+      </c>
+      <c r="O525">
+        <v>1.2</v>
+      </c>
+      <c r="P525">
+        <v>1.2</v>
+      </c>
+      <c r="Q525">
+        <v>1.05</v>
+      </c>
+      <c r="R525">
+        <v>0.16679850853156178</v>
+      </c>
+    </row>
+    <row r="527" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A527" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B526" s="5" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="527" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A527" t="s">
+      <c r="B527" s="5" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="528" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A528" t="s">
         <v>7</v>
       </c>
-      <c r="B527" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="528" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A528" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B528">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="529" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A529" t="s">
-        <v>2</v>
-      </c>
-      <c r="B529" t="s">
-        <v>294</v>
+      <c r="B528" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="529" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A529" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B529">
+        <v>1</v>
       </c>
     </row>
     <row r="530" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B530" t="s">
-        <v>4</v>
+        <v>295</v>
       </c>
     </row>
     <row r="531" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B531" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="532" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B532" t="s">
-        <v>236</v>
+        <v>6</v>
       </c>
     </row>
     <row r="533" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B533" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
     </row>
     <row r="534" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
+        <v>9</v>
+      </c>
+      <c r="B534" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="535" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A535" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="535" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A535" s="1" t="s">
+    <row r="536" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A536" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B535" s="1" t="s">
+      <c r="B536" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C535" s="5" t="s">
+      <c r="C536" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D535" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E535" s="5" t="s">
+      <c r="D536" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E536" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F535" s="5" t="s">
+      <c r="F536" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G535" s="5" t="s">
+      <c r="G536" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H535" s="5" t="s">
+      <c r="H536" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I535" s="5"/>
-      <c r="J535" s="5"/>
-      <c r="K535" s="5"/>
-      <c r="L535" s="5"/>
-      <c r="M535" s="5"/>
-      <c r="N535" s="5"/>
-      <c r="O535" s="5"/>
-      <c r="P535" s="5"/>
-      <c r="Q535" s="5"/>
-      <c r="R535" s="5"/>
-      <c r="S535" s="5"/>
-    </row>
-    <row r="536" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A536" s="28" t="str">
-        <f>B526</f>
+      <c r="I536" s="5"/>
+      <c r="J536" s="5"/>
+      <c r="K536" s="5"/>
+      <c r="L536" s="5"/>
+      <c r="M536" s="5"/>
+      <c r="N536" s="5"/>
+      <c r="O536" s="5"/>
+      <c r="P536" s="5"/>
+      <c r="Q536" s="5"/>
+      <c r="R536" s="5"/>
+      <c r="S536" s="5"/>
+    </row>
+    <row r="537" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A537" s="28" t="str">
+        <f>B527</f>
         <v>carbon dioxide, captured, at cement production plant, using monoethanolamine</v>
       </c>
-      <c r="B536" s="37">
-        <v>1</v>
-      </c>
-      <c r="C536" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D536" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F536" s="28" t="s">
+      <c r="B537" s="37">
+        <v>1</v>
+      </c>
+      <c r="C537" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D537" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="F537" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="G536" s="28" t="str">
-        <f>B529</f>
+      <c r="G537" s="28" t="str">
+        <f>B530</f>
         <v>carbon dioxide, captured</v>
-      </c>
-    </row>
-    <row r="537" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A537" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="B537" s="29">
-        <v>1</v>
-      </c>
-      <c r="C537" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D537" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F537" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="G537" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="538" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A538" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B538" s="29">
+        <v>1</v>
+      </c>
+      <c r="C538" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D538" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="F538" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G538" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="539" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A539" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="B538" s="37">
+      <c r="B539" s="37">
         <f>1.4/1000</f>
         <v>1.4E-3</v>
       </c>
-      <c r="C538" s="28" t="s">
+      <c r="C539" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D538" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F538" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="G538" s="28" t="s">
+      <c r="D539" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="F539" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G539" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="H538" s="28" t="s">
-        <v>226</v>
-      </c>
-      <c r="N538" s="29"/>
-    </row>
-    <row r="539" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A539" s="28" t="s">
+      <c r="H539" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="N539" s="29"/>
+    </row>
+    <row r="540" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A540" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="B539" s="29">
+      <c r="B540" s="29">
         <f>0.000355*1.25*(1/0.828)</f>
         <v>5.3592995169082129E-4</v>
       </c>
-      <c r="C539" s="28" t="s">
+      <c r="C540" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D539" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F539" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="G539" s="28" t="s">
+      <c r="D540" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="F540" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G540" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="H539" s="28" t="s">
-        <v>238</v>
-      </c>
-      <c r="N539" s="29"/>
-      <c r="P539" s="29"/>
-    </row>
-    <row r="540" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A540" t="s">
-        <v>317</v>
-      </c>
-      <c r="B540" s="29">
+      <c r="H540" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="N540" s="29"/>
+      <c r="P540" s="29"/>
+    </row>
+    <row r="541" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A541" t="s">
+        <v>318</v>
+      </c>
+      <c r="B541" s="29">
         <f>(3.76-0.11)/0.9</f>
         <v>4.0555555555555554</v>
       </c>
-      <c r="C540" s="28" t="s">
+      <c r="C541" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="D540" s="28" t="s">
+      <c r="D541" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F540" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="G540" s="28" t="s">
+      <c r="F541" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G541" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="H540" s="28" t="s">
-        <v>235</v>
-      </c>
-      <c r="N540" s="29"/>
-    </row>
-    <row r="541" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A541" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="B541" s="29">
-        <f>188/761*0.459/3.6</f>
-        <v>3.1498028909329831E-2</v>
-      </c>
-      <c r="C541" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D541" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F541" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="G541" s="28" t="s">
-        <v>24</v>
-      </c>
       <c r="H541" s="28" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="N541" s="29"/>
     </row>
@@ -11767,8 +11756,8 @@
         <v>34</v>
       </c>
       <c r="B542" s="29">
-        <f>123/761*0.459/3.6</f>
-        <v>2.0607752956636003E-2</v>
+        <f>188/761*0.459/3.6</f>
+        <v>3.1498028909329831E-2</v>
       </c>
       <c r="C542" s="28" t="s">
         <v>8</v>
@@ -11792,70 +11781,71 @@
         <v>34</v>
       </c>
       <c r="B543" s="29">
+        <f>123/761*0.459/3.6</f>
+        <v>2.0607752956636003E-2</v>
+      </c>
+      <c r="C543" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D543" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F543" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G543" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H543" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="N543" s="29"/>
+    </row>
+    <row r="544" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A544" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B544" s="29">
         <f>575/761*0.459/3.6</f>
         <v>9.63370565045992E-2</v>
       </c>
-      <c r="C543" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D543" s="28" t="s">
+      <c r="C544" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D544" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="F543" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="G543" s="28" t="s">
+      <c r="F544" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G544" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="H543" s="28" t="s">
-        <v>237</v>
-      </c>
-      <c r="N543" s="29"/>
-      <c r="Q543" s="30"/>
-    </row>
-    <row r="544" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A544" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="B544" s="29">
+      <c r="H544" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="N544" s="29"/>
+      <c r="Q544" s="30"/>
+    </row>
+    <row r="545" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A545" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="B545" s="29">
         <f>0.473</f>
         <v>0.47299999999999998</v>
       </c>
-      <c r="C544" s="28" t="s">
+      <c r="C545" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D544" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F544" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="G544" s="28" t="s">
+      <c r="D545" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="F545" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G545" s="28" t="s">
         <v>32</v>
-      </c>
-      <c r="H544" s="28" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="545" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A545" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="B545" s="29">
-        <f>-B538*0.227/(0.227+0.006)</f>
-        <v>-1.3639484978540772E-3</v>
-      </c>
-      <c r="C545" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="D545" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F545" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="G545" s="28" t="s">
-        <v>140</v>
       </c>
       <c r="H545" s="28" t="s">
         <v>231</v>
@@ -11863,35 +11853,38 @@
     </row>
     <row r="546" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A546" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="B546" s="29">
+        <f>-B539*0.227/(0.227+0.006)</f>
+        <v>-1.3639484978540772E-3</v>
+      </c>
+      <c r="C546" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="D546" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="F546" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G546" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="H546" s="28" t="s">
         <v>232</v>
       </c>
-      <c r="B546" s="37">
+    </row>
+    <row r="547" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A547" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="B547" s="37">
         <f>1.4/1000*(0.006/0.227+0.006)</f>
         <v>4.5404405286343617E-5</v>
       </c>
-      <c r="D546" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E546" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="F546" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="H546" s="28" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="547" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A547" s="28" t="s">
-        <v>234</v>
-      </c>
-      <c r="B547" s="29">
-        <f>B544/1000</f>
-        <v>4.7299999999999995E-4</v>
-      </c>
       <c r="D547" s="28" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="E547" s="28" t="s">
         <v>85</v>
@@ -11899,413 +11892,410 @@
       <c r="F547" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="G547" s="29"/>
-    </row>
-    <row r="549" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A549" s="1" t="s">
+      <c r="H547" s="28" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="548" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A548" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="B548" s="29">
+        <f>B545/1000</f>
+        <v>4.7299999999999995E-4</v>
+      </c>
+      <c r="D548" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="E548" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="F548" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G548" s="29"/>
+    </row>
+    <row r="550" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A550" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B549" s="5" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="550" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A550" t="s">
+      <c r="B550" s="5" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="551" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A551" t="s">
         <v>7</v>
       </c>
-      <c r="B550" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="551" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A551" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B551">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="552" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A552" t="s">
-        <v>2</v>
-      </c>
-      <c r="B552" t="s">
-        <v>294</v>
+      <c r="B551" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="552" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A552" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B552">
+        <v>1</v>
       </c>
     </row>
     <row r="553" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B553" t="s">
-        <v>4</v>
+        <v>295</v>
       </c>
     </row>
     <row r="554" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B554" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="555" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B555" t="s">
-        <v>236</v>
+        <v>6</v>
       </c>
     </row>
     <row r="556" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B556" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="557" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
+        <v>9</v>
+      </c>
+      <c r="B557" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="558" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A558" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="558" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A558" s="1" t="s">
+    <row r="559" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A559" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B558" s="1" t="s">
+      <c r="B559" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C558" s="5" t="s">
+      <c r="C559" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D558" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E558" s="5" t="s">
+      <c r="D559" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E559" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F558" s="5" t="s">
+      <c r="F559" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G558" s="5" t="s">
+      <c r="G559" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H558" s="5" t="s">
+      <c r="H559" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I558" s="5"/>
-      <c r="J558" s="5"/>
-      <c r="K558" s="5"/>
-      <c r="L558" s="5"/>
-      <c r="M558" s="5"/>
-      <c r="N558" s="5"/>
-      <c r="O558" s="5"/>
-      <c r="P558" s="5"/>
-      <c r="Q558" s="5"/>
-      <c r="R558" s="5"/>
-      <c r="S558" s="5"/>
-    </row>
-    <row r="559" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A559" s="28" t="str">
-        <f>B549</f>
+      <c r="I559" s="5"/>
+      <c r="J559" s="5"/>
+      <c r="K559" s="5"/>
+      <c r="L559" s="5"/>
+      <c r="M559" s="5"/>
+      <c r="N559" s="5"/>
+      <c r="O559" s="5"/>
+      <c r="P559" s="5"/>
+      <c r="Q559" s="5"/>
+      <c r="R559" s="5"/>
+      <c r="S559" s="5"/>
+    </row>
+    <row r="560" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A560" s="28" t="str">
+        <f>B550</f>
         <v>carbon dioxide, captured, at cement production plant, using direct separation</v>
       </c>
-      <c r="B559" s="28">
-        <v>1</v>
-      </c>
-      <c r="C559" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D559" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F559" s="28" t="s">
+      <c r="B560" s="28">
+        <v>1</v>
+      </c>
+      <c r="C560" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D560" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="F560" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="G559" s="28" t="str">
-        <f>B552</f>
+      <c r="G560" s="28" t="str">
+        <f>B553</f>
         <v>carbon dioxide, captured</v>
       </c>
     </row>
-    <row r="560" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A560" s="28" t="s">
+    <row r="561" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A561" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="B560" s="29">
-        <v>1</v>
-      </c>
-      <c r="C560" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D560" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E560" s="28"/>
-      <c r="F560" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="G560" t="s">
+      <c r="B561" s="29">
+        <v>1</v>
+      </c>
+      <c r="C561" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D561" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="E561" s="28"/>
+      <c r="F561" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G561" t="s">
         <v>98</v>
       </c>
-      <c r="H560" s="28"/>
-    </row>
-    <row r="561" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A561" s="26" t="s">
+      <c r="H561" s="28"/>
+    </row>
+    <row r="562" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A562" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="B561" s="32">
+      <c r="B562" s="32">
         <f>77*1/0.558/1000</f>
         <v>0.13799283154121864</v>
       </c>
-      <c r="C561" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D561" s="26" t="s">
+      <c r="C562" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D562" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="F561" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G561" s="26" t="s">
+      <c r="F562" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G562" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="H561" s="26" t="s">
-        <v>240</v>
-      </c>
-      <c r="N561" s="32"/>
-    </row>
-    <row r="564" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A564" s="1" t="s">
+      <c r="H562" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="N562" s="32"/>
+    </row>
+    <row r="565" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A565" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B564" s="5" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="565" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A565" t="s">
+      <c r="B565" s="5" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="566" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A566" t="s">
         <v>7</v>
       </c>
-      <c r="B565" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="566" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A566" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B566">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="567" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A567" t="s">
-        <v>2</v>
-      </c>
-      <c r="B567" t="s">
-        <v>294</v>
+      <c r="B566" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="567" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A567" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B567">
+        <v>1</v>
       </c>
     </row>
     <row r="568" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B568" t="s">
-        <v>4</v>
+        <v>295</v>
       </c>
     </row>
     <row r="569" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B569" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="570" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B570" t="s">
-        <v>236</v>
+        <v>6</v>
       </c>
     </row>
     <row r="571" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B571" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="572" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
+        <v>9</v>
+      </c>
+      <c r="B572" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="573" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A573" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="573" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A573" s="1" t="s">
+    <row r="574" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A574" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B573" s="1" t="s">
+      <c r="B574" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C573" s="5" t="s">
+      <c r="C574" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D573" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E573" s="5" t="s">
+      <c r="D574" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E574" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F573" s="5" t="s">
+      <c r="F574" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G573" s="5" t="s">
+      <c r="G574" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H573" s="5" t="s">
+      <c r="H574" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I573" s="5"/>
-      <c r="J573" s="5"/>
-      <c r="K573" s="5"/>
-      <c r="L573" s="5"/>
-      <c r="M573" s="5"/>
-      <c r="N573" s="5"/>
-      <c r="O573" s="5"/>
-      <c r="P573" s="5"/>
-      <c r="Q573" s="5"/>
-      <c r="R573" s="5"/>
-      <c r="S573" s="5"/>
-    </row>
-    <row r="574" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A574" s="28" t="str">
-        <f>B564</f>
+      <c r="I574" s="5"/>
+      <c r="J574" s="5"/>
+      <c r="K574" s="5"/>
+      <c r="L574" s="5"/>
+      <c r="M574" s="5"/>
+      <c r="N574" s="5"/>
+      <c r="O574" s="5"/>
+      <c r="P574" s="5"/>
+      <c r="Q574" s="5"/>
+      <c r="R574" s="5"/>
+      <c r="S574" s="5"/>
+    </row>
+    <row r="575" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A575" s="28" t="str">
+        <f>B565</f>
         <v>carbon dioxide, captured, at cement production plant, using oxyfuel</v>
       </c>
-      <c r="B574" s="28">
-        <v>1</v>
-      </c>
-      <c r="C574" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D574" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F574" s="28" t="s">
+      <c r="B575" s="28">
+        <v>1</v>
+      </c>
+      <c r="C575" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D575" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="F575" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="G574" s="28" t="str">
-        <f>B567</f>
+      <c r="G575" s="28" t="str">
+        <f>B568</f>
         <v>carbon dioxide, captured</v>
       </c>
     </row>
-    <row r="575" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A575" s="28" t="s">
+    <row r="576" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A576" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="B575" s="29">
-        <v>1</v>
-      </c>
-      <c r="C575" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D575" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E575" s="28"/>
-      <c r="F575" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="G575" t="s">
+      <c r="B576" s="29">
+        <v>1</v>
+      </c>
+      <c r="C576" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D576" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="E576" s="28"/>
+      <c r="F576" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G576" t="s">
         <v>98</v>
       </c>
-      <c r="H575" s="28"/>
-    </row>
-    <row r="576" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A576" t="s">
-        <v>248</v>
-      </c>
-      <c r="B576" s="6">
-        <f>B574*32/44/(1-0.11)</f>
-        <v>0.81716036772216549</v>
-      </c>
-      <c r="C576" t="s">
-        <v>26</v>
-      </c>
-      <c r="D576" t="s">
-        <v>6</v>
-      </c>
-      <c r="F576" t="s">
-        <v>16</v>
-      </c>
-      <c r="G576" t="s">
-        <v>246</v>
-      </c>
-      <c r="H576" t="s">
-        <v>242</v>
-      </c>
+      <c r="H576" s="28"/>
     </row>
     <row r="577" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
+        <v>249</v>
+      </c>
+      <c r="B577" s="6">
+        <f>B575*32/44/(1-0.11)</f>
+        <v>0.81716036772216549</v>
+      </c>
+      <c r="C577" t="s">
+        <v>26</v>
+      </c>
+      <c r="D577" t="s">
+        <v>6</v>
+      </c>
+      <c r="F577" t="s">
+        <v>16</v>
+      </c>
+      <c r="G577" t="s">
+        <v>247</v>
+      </c>
+      <c r="H577" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="578" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A578" t="s">
         <v>34</v>
       </c>
-      <c r="B577" s="6">
+      <c r="B578" s="6">
         <f>(122-182-62)/758*0.459/3.6</f>
         <v>-2.0521108179419524E-2</v>
       </c>
-      <c r="C577" t="s">
-        <v>8</v>
-      </c>
-      <c r="D577" t="s">
+      <c r="C578" t="s">
+        <v>8</v>
+      </c>
+      <c r="D578" t="s">
         <v>23</v>
       </c>
-      <c r="F577" t="s">
-        <v>16</v>
-      </c>
-      <c r="G577" t="s">
+      <c r="F578" t="s">
+        <v>16</v>
+      </c>
+      <c r="G578" t="s">
         <v>24</v>
       </c>
-      <c r="H577" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="578" spans="1:22" ht="16.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A578" t="s">
+      <c r="H578" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="579" spans="1:22" ht="16.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A579" t="s">
         <v>34</v>
       </c>
-      <c r="B578" s="6">
+      <c r="B579" s="6">
         <f>59/758*0.459/3.6</f>
         <v>9.9241424802110813E-3</v>
       </c>
-      <c r="C578" t="s">
-        <v>8</v>
-      </c>
-      <c r="D578" t="s">
-        <v>23</v>
-      </c>
-      <c r="F578" t="s">
-        <v>16</v>
-      </c>
-      <c r="G578" t="s">
-        <v>24</v>
-      </c>
-      <c r="H578" s="26" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="579" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A579" t="s">
-        <v>34</v>
-      </c>
-      <c r="B579" s="6">
-        <f>440/3600</f>
-        <v>0.12222222222222222</v>
-      </c>
       <c r="C579" t="s">
         <v>8</v>
       </c>
@@ -12318,320 +12308,318 @@
       <c r="G579" t="s">
         <v>24</v>
       </c>
-      <c r="H579" t="s">
+      <c r="H579" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="M579" s="27"/>
-      <c r="N579" s="31"/>
     </row>
     <row r="580" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
         <v>34</v>
       </c>
       <c r="B580" s="6">
+        <f>440/3600</f>
+        <v>0.12222222222222222</v>
+      </c>
+      <c r="C580" t="s">
+        <v>8</v>
+      </c>
+      <c r="D580" t="s">
+        <v>23</v>
+      </c>
+      <c r="F580" t="s">
+        <v>16</v>
+      </c>
+      <c r="G580" t="s">
+        <v>24</v>
+      </c>
+      <c r="H580" t="s">
+        <v>246</v>
+      </c>
+      <c r="M580" s="27"/>
+      <c r="N580" s="31"/>
+    </row>
+    <row r="581" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A581" t="s">
+        <v>34</v>
+      </c>
+      <c r="B581" s="6">
         <f>0.03/3600</f>
         <v>8.3333333333333337E-6</v>
       </c>
-      <c r="C580" t="s">
-        <v>8</v>
-      </c>
-      <c r="D580" t="s">
+      <c r="C581" t="s">
+        <v>8</v>
+      </c>
+      <c r="D581" t="s">
         <v>23</v>
       </c>
-      <c r="F580" t="s">
-        <v>16</v>
-      </c>
-      <c r="G580" t="s">
+      <c r="F581" t="s">
+        <v>16</v>
+      </c>
+      <c r="G581" t="s">
         <v>24</v>
       </c>
-      <c r="H580" t="s">
-        <v>247</v>
-      </c>
-      <c r="M580" s="27"/>
-      <c r="N580" s="31"/>
-    </row>
-    <row r="582" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A582" s="1" t="s">
+      <c r="H581" t="s">
+        <v>248</v>
+      </c>
+      <c r="M581" s="27"/>
+      <c r="N581" s="31"/>
+    </row>
+    <row r="583" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A583" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B582" s="34" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="583" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A583" t="s">
-        <v>9</v>
-      </c>
-      <c r="B583" s="35" t="s">
-        <v>254</v>
+      <c r="B583" s="34" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="584" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B584" s="35" t="s">
-        <v>8</v>
+        <v>255</v>
       </c>
     </row>
     <row r="585" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B585" s="35" t="s">
-        <v>294</v>
+        <v>8</v>
       </c>
     </row>
     <row r="586" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B586" s="35" t="s">
-        <v>6</v>
+        <v>295</v>
       </c>
     </row>
     <row r="587" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A587" s="5" t="s">
+      <c r="A587" t="s">
+        <v>5</v>
+      </c>
+      <c r="B587" s="35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="588" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A588" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B587" s="35"/>
-    </row>
-    <row r="588" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A588" s="1" t="s">
+      <c r="B588" s="35"/>
+    </row>
+    <row r="589" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A589" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B588" s="34" t="s">
+      <c r="B589" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="C588" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D588" s="1" t="s">
+      <c r="C589" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D589" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E588" s="1" t="s">
+      <c r="E589" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F588" s="1" t="s">
+      <c r="F589" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G588" s="1" t="s">
+      <c r="G589" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H588" s="1"/>
-      <c r="I588" s="1"/>
-      <c r="J588" s="1"/>
-      <c r="K588" s="1"/>
-      <c r="L588" s="1"/>
-      <c r="M588" s="1"/>
-      <c r="N588" s="1"/>
-      <c r="O588" s="1"/>
-      <c r="P588" s="1"/>
-      <c r="Q588" s="1"/>
-      <c r="R588" s="1"/>
-      <c r="S588" s="1"/>
-      <c r="T588" s="1"/>
-      <c r="U588" s="1"/>
-      <c r="V588" s="1"/>
-    </row>
-    <row r="589" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A589" t="str">
-        <f>B582</f>
+      <c r="H589" s="1"/>
+      <c r="I589" s="1"/>
+      <c r="J589" s="1"/>
+      <c r="K589" s="1"/>
+      <c r="L589" s="1"/>
+      <c r="M589" s="1"/>
+      <c r="N589" s="1"/>
+      <c r="O589" s="1"/>
+      <c r="P589" s="1"/>
+      <c r="Q589" s="1"/>
+      <c r="R589" s="1"/>
+      <c r="S589" s="1"/>
+      <c r="T589" s="1"/>
+      <c r="U589" s="1"/>
+      <c r="V589" s="1"/>
+    </row>
+    <row r="590" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A590" t="str">
+        <f>B583</f>
         <v>carbon dioxide, captured and stored, by land-use change</v>
       </c>
-      <c r="B589" s="35">
-        <v>1</v>
-      </c>
-      <c r="C589" t="str">
+      <c r="B590" s="35">
+        <v>1</v>
+      </c>
+      <c r="C590" t="str">
+        <f>B587</f>
+        <v>kilogram</v>
+      </c>
+      <c r="E590" t="str">
+        <f>B585</f>
+        <v>RER</v>
+      </c>
+      <c r="F590" t="s">
+        <v>15</v>
+      </c>
+      <c r="G590" t="str">
         <f>B586</f>
-        <v>kilogram</v>
-      </c>
-      <c r="E589" t="str">
-        <f>B584</f>
-        <v>RER</v>
-      </c>
-      <c r="F589" t="s">
-        <v>15</v>
-      </c>
-      <c r="G589" t="str">
-        <f>B585</f>
         <v>carbon dioxide, captured</v>
       </c>
     </row>
-    <row r="590" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A590" t="s">
-        <v>255</v>
-      </c>
-      <c r="B590" s="36">
-        <v>1</v>
-      </c>
-      <c r="C590" t="s">
-        <v>6</v>
-      </c>
-      <c r="D590" t="s">
+    <row r="591" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A591" t="s">
         <v>256</v>
       </c>
-      <c r="F590" t="s">
+      <c r="B591" s="36">
+        <v>1</v>
+      </c>
+      <c r="C591" t="s">
+        <v>6</v>
+      </c>
+      <c r="D591" t="s">
+        <v>257</v>
+      </c>
+      <c r="F591" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="592" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A592" s="1" t="s">
+    <row r="593" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A593" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B592" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="M592" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="593" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A593" t="s">
-        <v>7</v>
-      </c>
-      <c r="B593" t="s">
-        <v>8</v>
+      <c r="B593" s="1" t="s">
+        <v>282</v>
       </c>
       <c r="M593" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="594" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
-        <v>1</v>
-      </c>
-      <c r="B594">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="B594" t="s">
+        <v>8</v>
       </c>
       <c r="M594" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="595" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
-        <v>2</v>
-      </c>
-      <c r="B595" t="s">
-        <v>294</v>
+        <v>1</v>
+      </c>
+      <c r="B595">
+        <v>1</v>
       </c>
       <c r="M595" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="596" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A596" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B596" t="s">
-        <v>4</v>
+        <v>295</v>
       </c>
       <c r="M596" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="597" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B597" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M597" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="598" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B598" t="s">
-        <v>282</v>
+        <v>6</v>
       </c>
       <c r="M598" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="599" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B599" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="M599" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="600" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A600" s="1" t="s">
-        <v>10</v>
+    <row r="600" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A600" t="s">
+        <v>18</v>
+      </c>
+      <c r="B600" t="s">
+        <v>258</v>
       </c>
       <c r="M600" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="601" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A601" t="s">
+    <row r="601" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A601" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M601" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="602" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A602" t="s">
         <v>11</v>
       </c>
-      <c r="B601" t="s">
+      <c r="B602" t="s">
         <v>12</v>
       </c>
-      <c r="C601" t="s">
+      <c r="C602" t="s">
         <v>7</v>
       </c>
-      <c r="D601" t="s">
-        <v>5</v>
-      </c>
-      <c r="E601" t="s">
+      <c r="D602" t="s">
+        <v>5</v>
+      </c>
+      <c r="E602" t="s">
         <v>13</v>
       </c>
-      <c r="F601" t="s">
+      <c r="F602" t="s">
         <v>3</v>
       </c>
-      <c r="G601" t="s">
+      <c r="G602" t="s">
         <v>172</v>
       </c>
-      <c r="H601" t="s">
+      <c r="H602" t="s">
         <v>9</v>
       </c>
-      <c r="I601" t="s">
+      <c r="I602" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="602" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A602" t="s">
+    <row r="603" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A603" t="s">
         <v>186</v>
       </c>
-      <c r="B602">
+      <c r="B603">
         <v>1.2300000000000001E-4</v>
-      </c>
-      <c r="D602" t="s">
-        <v>6</v>
-      </c>
-      <c r="E602" t="s">
-        <v>85</v>
-      </c>
-      <c r="F602" t="s">
-        <v>20</v>
-      </c>
-      <c r="G602">
-        <v>0</v>
-      </c>
-      <c r="H602" t="s">
-        <v>258</v>
-      </c>
-      <c r="I602" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="603" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A603" t="s">
-        <v>232</v>
-      </c>
-      <c r="B603" s="38">
-        <v>6.0000000000000002E-6</v>
       </c>
       <c r="D603" t="s">
         <v>6</v>
@@ -12646,24 +12634,24 @@
         <v>0</v>
       </c>
       <c r="H603" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I603" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="604" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A604" t="s">
-        <v>259</v>
-      </c>
-      <c r="B604">
-        <v>8.3199999999999996E-2</v>
+        <v>233</v>
+      </c>
+      <c r="B604" s="38">
+        <v>6.0000000000000002E-6</v>
       </c>
       <c r="D604" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="E604" t="s">
-        <v>260</v>
+        <v>85</v>
       </c>
       <c r="F604" t="s">
         <v>20</v>
@@ -12672,25 +12660,24 @@
         <v>0</v>
       </c>
       <c r="H604" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="I604" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="605" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A605" t="s">
-        <v>234</v>
-      </c>
-      <c r="B605" s="33">
-        <f>((B604*1000)-(600*3.78541/1000))/1000</f>
-        <v>8.0928753999999992E-2</v>
+        <v>260</v>
+      </c>
+      <c r="B605">
+        <v>8.3199999999999996E-2</v>
       </c>
       <c r="D605" t="s">
         <v>49</v>
       </c>
       <c r="E605" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F605" t="s">
         <v>20</v>
@@ -12699,40 +12686,40 @@
         <v>0</v>
       </c>
       <c r="H605" t="s">
+        <v>262</v>
+      </c>
+      <c r="I605" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="606" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A606" t="s">
+        <v>235</v>
+      </c>
+      <c r="B606" s="33">
+        <f>((B605*1000)-(600*3.78541/1000))/1000</f>
+        <v>8.0928753999999992E-2</v>
+      </c>
+      <c r="D606" t="s">
+        <v>49</v>
+      </c>
+      <c r="E606" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="606" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A606" t="str">
-        <f>B592</f>
-        <v>carbon dioxide, captured and stored, at wood burning power plant, pipeline 200km, storage 1000m</v>
-      </c>
-      <c r="B606">
-        <v>1</v>
-      </c>
-      <c r="C606" t="s">
-        <v>8</v>
-      </c>
-      <c r="D606" t="s">
-        <v>6</v>
-      </c>
       <c r="F606" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G606">
         <v>0</v>
       </c>
       <c r="H606" t="s">
-        <v>183</v>
-      </c>
-      <c r="I606" t="str">
-        <f>B595</f>
-        <v>carbon dioxide, captured</v>
-      </c>
-    </row>
-    <row r="607" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A607" s="28" t="s">
-        <v>97</v>
+        <v>264</v>
+      </c>
+    </row>
+    <row r="607" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A607" t="str">
+        <f>B593</f>
+        <v>carbon dioxide, captured and stored, at wood burning power plant, pipeline 200km, storage 1000m</v>
       </c>
       <c r="B607">
         <v>1</v>
@@ -12743,11 +12730,8 @@
       <c r="D607" t="s">
         <v>6</v>
       </c>
-      <c r="E607" t="s">
-        <v>264</v>
-      </c>
       <c r="F607" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G607">
         <v>0</v>
@@ -12755,45 +12739,47 @@
       <c r="H607" t="s">
         <v>183</v>
       </c>
-      <c r="I607" t="s">
+      <c r="I607" t="str">
+        <f>B596</f>
+        <v>carbon dioxide, captured</v>
+      </c>
+    </row>
+    <row r="608" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A608" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B608">
+        <v>1</v>
+      </c>
+      <c r="C608" t="s">
+        <v>8</v>
+      </c>
+      <c r="D608" t="s">
+        <v>6</v>
+      </c>
+      <c r="E608" t="s">
+        <v>265</v>
+      </c>
+      <c r="F608" t="s">
+        <v>16</v>
+      </c>
+      <c r="G608">
+        <v>0</v>
+      </c>
+      <c r="H608" t="s">
+        <v>183</v>
+      </c>
+      <c r="I608" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="608" spans="1:14" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A608" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="B608" s="29">
-        <f>188/761*0.459/3.6</f>
-        <v>3.1498028909329831E-2</v>
-      </c>
-      <c r="C608" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D608" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F608" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="G608" s="28">
-        <v>0</v>
-      </c>
-      <c r="H608" s="28" t="s">
-        <v>227</v>
-      </c>
-      <c r="I608" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="N608" s="29"/>
     </row>
     <row r="609" spans="1:17" s="28" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A609" s="28" t="s">
         <v>34</v>
       </c>
       <c r="B609" s="29">
-        <f>123/761*0.459/3.6</f>
-        <v>2.0607752956636003E-2</v>
+        <f>188/761*0.459/3.6</f>
+        <v>3.1498028909329831E-2</v>
       </c>
       <c r="C609" s="28" t="s">
         <v>8</v>
@@ -12820,74 +12806,73 @@
         <v>34</v>
       </c>
       <c r="B610" s="29">
+        <f>123/761*0.459/3.6</f>
+        <v>2.0607752956636003E-2</v>
+      </c>
+      <c r="C610" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D610" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F610" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G610" s="28">
+        <v>0</v>
+      </c>
+      <c r="H610" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="I610" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="N610" s="29"/>
+    </row>
+    <row r="611" spans="1:17" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A611" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B611" s="29">
         <f>575/761*0.459/3.6</f>
         <v>9.63370565045992E-2</v>
       </c>
-      <c r="C610" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D610" s="28" t="s">
+      <c r="C611" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D611" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="F610" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="G610" s="28">
+      <c r="F611" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G611" s="28">
         <v>0</v>
       </c>
-      <c r="H610" s="28" t="s">
-        <v>237</v>
-      </c>
-      <c r="I610" s="28" t="s">
+      <c r="H611" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="I611" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="N610" s="29"/>
-      <c r="Q610" s="30"/>
-    </row>
-    <row r="611" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A611" t="s">
-        <v>284</v>
-      </c>
-      <c r="B611">
-        <v>1.9099999999999998E-9</v>
-      </c>
-      <c r="C611" t="s">
-        <v>8</v>
-      </c>
-      <c r="D611" t="s">
-        <v>5</v>
-      </c>
-      <c r="E611" t="s">
-        <v>264</v>
-      </c>
-      <c r="F611" t="s">
-        <v>16</v>
-      </c>
-      <c r="G611">
-        <v>0</v>
-      </c>
-      <c r="H611" t="s">
-        <v>265</v>
-      </c>
-      <c r="I611" t="s">
-        <v>285</v>
-      </c>
+      <c r="N611" s="29"/>
+      <c r="Q611" s="30"/>
     </row>
     <row r="612" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A612" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="B612">
-        <v>1.15E-8</v>
+        <v>1.9099999999999998E-9</v>
       </c>
       <c r="C612" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D612" t="s">
         <v>5</v>
       </c>
       <c r="E612" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F612" t="s">
         <v>16</v>
@@ -12896,27 +12881,27 @@
         <v>0</v>
       </c>
       <c r="H612" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I612" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
     </row>
     <row r="613" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A613" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B613">
-        <v>8.2600000000000002E-5</v>
+        <v>1.15E-8</v>
       </c>
       <c r="C613" t="s">
         <v>17</v>
       </c>
       <c r="D613" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E613" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F613" t="s">
         <v>16</v>
@@ -12925,27 +12910,27 @@
         <v>0</v>
       </c>
       <c r="H613" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="I613" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="614" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A614" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B614">
-        <v>1.9099999999999998E-9</v>
+        <v>8.2600000000000002E-5</v>
       </c>
       <c r="C614" t="s">
         <v>17</v>
       </c>
       <c r="D614" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E614" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F614" t="s">
         <v>16</v>
@@ -12954,18 +12939,18 @@
         <v>0</v>
       </c>
       <c r="H614" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="I614" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="615" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A615" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B615">
-        <v>6.4400000000000005E-10</v>
+        <v>1.9099999999999998E-9</v>
       </c>
       <c r="C615" t="s">
         <v>17</v>
@@ -12974,7 +12959,7 @@
         <v>5</v>
       </c>
       <c r="E615" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F615" t="s">
         <v>16</v>
@@ -12983,27 +12968,27 @@
         <v>0</v>
       </c>
       <c r="H615" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I615" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="616" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A616" t="s">
-        <v>90</v>
-      </c>
-      <c r="B616" s="38">
-        <v>1.4E-3</v>
+        <v>275</v>
+      </c>
+      <c r="B616">
+        <v>6.4400000000000005E-10</v>
       </c>
       <c r="C616" t="s">
         <v>17</v>
       </c>
       <c r="D616" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E616" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F616" t="s">
         <v>16</v>
@@ -13011,28 +12996,28 @@
       <c r="G616">
         <v>0</v>
       </c>
-      <c r="H616" s="28" t="s">
-        <v>226</v>
+      <c r="H616" t="s">
+        <v>276</v>
       </c>
       <c r="I616" t="s">
-        <v>141</v>
+        <v>277</v>
       </c>
     </row>
     <row r="617" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A617" t="s">
-        <v>277</v>
-      </c>
-      <c r="B617">
-        <v>1.3399999999999999E-8</v>
+        <v>90</v>
+      </c>
+      <c r="B617" s="38">
+        <v>1.4E-3</v>
       </c>
       <c r="C617" t="s">
         <v>17</v>
       </c>
       <c r="D617" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E617" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F617" t="s">
         <v>16</v>
@@ -13040,28 +13025,28 @@
       <c r="G617">
         <v>0</v>
       </c>
-      <c r="H617" t="s">
-        <v>278</v>
+      <c r="H617" s="28" t="s">
+        <v>227</v>
       </c>
       <c r="I617" t="s">
-        <v>279</v>
+        <v>141</v>
       </c>
     </row>
     <row r="618" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A618" t="s">
-        <v>91</v>
+        <v>278</v>
       </c>
       <c r="B618">
-        <v>3.0400000000000002E-4</v>
+        <v>1.3399999999999999E-8</v>
       </c>
       <c r="C618" t="s">
         <v>17</v>
       </c>
       <c r="D618" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E618" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F618" t="s">
         <v>16</v>
@@ -13070,28 +13055,27 @@
         <v>0</v>
       </c>
       <c r="H618" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="I618" t="s">
-        <v>142</v>
+        <v>280</v>
       </c>
     </row>
     <row r="619" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A619" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="B619">
-        <f>-1*B616</f>
-        <v>-1.4E-3</v>
+        <v>3.0400000000000002E-4</v>
       </c>
       <c r="C619" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D619" t="s">
         <v>6</v>
       </c>
       <c r="E619" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="F619" t="s">
         <v>16</v>
@@ -13100,298 +13084,292 @@
         <v>0</v>
       </c>
       <c r="H619" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="I619" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="620" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A620" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="B620">
-        <v>1</v>
+        <f>-1*B617</f>
+        <v>-1.4E-3</v>
+      </c>
+      <c r="C620" t="s">
+        <v>21</v>
       </c>
       <c r="D620" t="s">
         <v>6</v>
       </c>
       <c r="E620" t="s">
-        <v>37</v>
+        <v>281</v>
       </c>
       <c r="F620" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G620">
         <v>0</v>
       </c>
       <c r="H620" t="s">
-        <v>283</v>
-      </c>
-      <c r="M620" t="s">
+        <v>259</v>
+      </c>
+      <c r="I620" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="621" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A621" t="s">
+        <v>39</v>
+      </c>
+      <c r="B621">
+        <v>1</v>
+      </c>
+      <c r="D621" t="s">
+        <v>6</v>
+      </c>
+      <c r="E621" t="s">
+        <v>37</v>
+      </c>
+      <c r="F621" t="s">
+        <v>20</v>
+      </c>
+      <c r="G621">
+        <v>0</v>
+      </c>
+      <c r="H621" t="s">
+        <v>284</v>
+      </c>
+      <c r="M621" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="622" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A622" s="1" t="s">
+    <row r="623" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A623" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B622" s="1" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="623" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A623" t="s">
-        <v>1</v>
-      </c>
-      <c r="B623">
-        <v>1</v>
+      <c r="B623" s="1" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="624" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A624" t="s">
-        <v>2</v>
-      </c>
-      <c r="B624" t="s">
-        <v>294</v>
+        <v>1</v>
+      </c>
+      <c r="B624">
+        <v>1</v>
       </c>
     </row>
     <row r="625" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A625" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B625" t="s">
-        <v>4</v>
+        <v>295</v>
       </c>
     </row>
     <row r="626" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A626" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B626" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="627" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A627" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B627" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="628" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A628" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B628" t="s">
-        <v>308</v>
+        <v>8</v>
       </c>
     </row>
     <row r="629" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A629" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B629" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="630" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A630" s="1" t="s">
+    <row r="630" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A630" t="s">
+        <v>9</v>
+      </c>
+      <c r="B630" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="631" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A631" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="631" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A631" s="5" t="s">
+    <row r="632" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A632" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B631" s="5" t="s">
+      <c r="B632" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C631" s="5" t="s">
+      <c r="C632" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D631" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E631" s="5" t="s">
+      <c r="D632" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E632" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F631" s="5" t="s">
+      <c r="F632" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G631" s="5" t="s">
+      <c r="G632" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H631" s="5" t="s">
+      <c r="H632" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I631" s="5" t="s">
+      <c r="I632" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="J631" s="5" t="s">
+      <c r="J632" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="K631" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="L631" s="5" t="s">
+      <c r="K632" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="M631" s="5" t="s">
+      <c r="L632" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="M632" s="5" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A632" t="str">
-        <f>B622</f>
+    <row r="633" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A633" t="str">
+        <f>B623</f>
         <v>carbon dioxide, captured and stored, from a hydrogen production plant using steam methane reforming of biomethane</v>
       </c>
-      <c r="B632">
-        <v>1</v>
-      </c>
-      <c r="C632" t="s">
-        <v>8</v>
-      </c>
-      <c r="D632" t="s">
-        <v>6</v>
-      </c>
-      <c r="F632" t="s">
+      <c r="B633">
+        <v>1</v>
+      </c>
+      <c r="C633" t="s">
+        <v>8</v>
+      </c>
+      <c r="D633" t="s">
+        <v>6</v>
+      </c>
+      <c r="F633" t="s">
         <v>15</v>
       </c>
-      <c r="G632" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="633" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A633" t="s">
+      <c r="G633" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="634" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A634" t="s">
         <v>34</v>
       </c>
-      <c r="B633" s="23">
+      <c r="B634" s="23">
         <f>AVERAGE(0.15,0.25)</f>
         <v>0.2</v>
       </c>
-      <c r="C633" t="s">
-        <v>8</v>
-      </c>
-      <c r="D633" t="s">
+      <c r="C634" t="s">
+        <v>8</v>
+      </c>
+      <c r="D634" t="s">
         <v>23</v>
       </c>
-      <c r="F633" t="s">
-        <v>16</v>
-      </c>
-      <c r="G633" t="s">
+      <c r="F634" t="s">
+        <v>16</v>
+      </c>
+      <c r="G634" t="s">
         <v>24</v>
       </c>
-      <c r="H633" t="s">
-        <v>310</v>
-      </c>
-      <c r="I633">
-        <v>5</v>
-      </c>
-      <c r="J633" s="23">
-        <f>B633</f>
+      <c r="H634" t="s">
+        <v>311</v>
+      </c>
+      <c r="I634">
+        <v>5</v>
+      </c>
+      <c r="J634" s="23">
+        <f>B634</f>
         <v>0.2</v>
       </c>
-      <c r="K633">
+      <c r="K634">
         <v>0.15</v>
       </c>
-      <c r="L633">
+      <c r="L634">
         <v>0.25</v>
       </c>
     </row>
-    <row r="634" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A634" t="s">
+    <row r="635" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A635" t="s">
         <v>31</v>
       </c>
-      <c r="B634">
+      <c r="B635">
         <f>AVERAGE(1,2)</f>
         <v>1.5</v>
       </c>
-      <c r="C634" t="s">
+      <c r="C635" t="s">
         <v>131</v>
       </c>
-      <c r="D634" t="s">
-        <v>6</v>
-      </c>
-      <c r="F634" t="s">
-        <v>16</v>
-      </c>
-      <c r="G634" t="s">
+      <c r="D635" t="s">
+        <v>6</v>
+      </c>
+      <c r="F635" t="s">
+        <v>16</v>
+      </c>
+      <c r="G635" t="s">
         <v>32</v>
       </c>
-      <c r="H634" t="s">
-        <v>311</v>
-      </c>
-      <c r="I634">
-        <v>5</v>
-      </c>
-      <c r="J634" s="23">
-        <f>B634</f>
+      <c r="H635" t="s">
+        <v>312</v>
+      </c>
+      <c r="I635">
+        <v>5</v>
+      </c>
+      <c r="J635" s="23">
+        <f>B635</f>
         <v>1.5</v>
       </c>
-      <c r="K634">
-        <v>1</v>
-      </c>
-      <c r="L634">
+      <c r="K635">
+        <v>1</v>
+      </c>
+      <c r="L635">
         <v>2</v>
       </c>
     </row>
-    <row r="635" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A635" t="s">
+    <row r="636" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A636" t="s">
         <v>34</v>
       </c>
-      <c r="B635">
+      <c r="B636">
         <f>AVERAGE(0.1,0.15)</f>
         <v>0.125</v>
       </c>
-      <c r="C635" t="s">
-        <v>8</v>
-      </c>
-      <c r="D635" t="s">
+      <c r="C636" t="s">
+        <v>8</v>
+      </c>
+      <c r="D636" t="s">
         <v>23</v>
       </c>
-      <c r="F635" t="s">
-        <v>16</v>
-      </c>
-      <c r="G635" t="s">
+      <c r="F636" t="s">
+        <v>16</v>
+      </c>
+      <c r="G636" t="s">
         <v>24</v>
-      </c>
-      <c r="H635" t="s">
-        <v>312</v>
-      </c>
-      <c r="I635">
-        <v>5</v>
-      </c>
-      <c r="J635" s="23">
-        <f>B635</f>
-        <v>0.125</v>
-      </c>
-      <c r="K635">
-        <v>0.1</v>
-      </c>
-      <c r="L635">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="636" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A636" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B636">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="C636" t="s">
-        <v>17</v>
-      </c>
-      <c r="D636" t="s">
-        <v>6</v>
-      </c>
-      <c r="F636" t="s">
-        <v>16</v>
-      </c>
-      <c r="G636" s="15" t="s">
-        <v>141</v>
       </c>
       <c r="H636" t="s">
         <v>313</v>
@@ -13401,84 +13379,97 @@
       </c>
       <c r="J636" s="23">
         <f>B636</f>
+        <v>0.125</v>
+      </c>
+      <c r="K636">
+        <v>0.1</v>
+      </c>
+      <c r="L636">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="637" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A637" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B637">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="K636">
+      <c r="C637" t="s">
+        <v>17</v>
+      </c>
+      <c r="D637" t="s">
+        <v>6</v>
+      </c>
+      <c r="F637" t="s">
+        <v>16</v>
+      </c>
+      <c r="G637" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="H637" t="s">
+        <v>314</v>
+      </c>
+      <c r="I637">
+        <v>5</v>
+      </c>
+      <c r="J637" s="23">
+        <f>B637</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K637">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="L636">
+      <c r="L637">
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="637" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A637" t="s">
+    <row r="638" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A638" t="s">
         <v>34</v>
       </c>
-      <c r="B637">
+      <c r="B638">
         <f>AVERAGE(0.08,0.12)</f>
         <v>0.1</v>
       </c>
-      <c r="C637" t="s">
-        <v>8</v>
-      </c>
-      <c r="D637" t="s">
+      <c r="C638" t="s">
+        <v>8</v>
+      </c>
+      <c r="D638" t="s">
         <v>23</v>
       </c>
-      <c r="F637" t="s">
-        <v>16</v>
-      </c>
-      <c r="G637" t="s">
+      <c r="F638" t="s">
+        <v>16</v>
+      </c>
+      <c r="G638" t="s">
         <v>24</v>
-      </c>
-      <c r="H637" t="s">
-        <v>314</v>
-      </c>
-      <c r="I637">
-        <v>5</v>
-      </c>
-      <c r="J637" s="23">
-        <f>B637</f>
-        <v>0.1</v>
-      </c>
-      <c r="K637">
-        <v>0.08</v>
-      </c>
-      <c r="L637">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="638" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A638" t="s">
-        <v>42</v>
-      </c>
-      <c r="B638" s="6">
-        <v>1.2E-5</v>
-      </c>
-      <c r="C638" t="s">
-        <v>17</v>
-      </c>
-      <c r="D638" t="s">
-        <v>6</v>
-      </c>
-      <c r="F638" t="s">
-        <v>16</v>
-      </c>
-      <c r="G638" t="s">
-        <v>30</v>
       </c>
       <c r="H638" t="s">
         <v>315</v>
       </c>
+      <c r="I638">
+        <v>5</v>
+      </c>
+      <c r="J638" s="23">
+        <f>B638</f>
+        <v>0.1</v>
+      </c>
+      <c r="K638">
+        <v>0.08</v>
+      </c>
+      <c r="L638">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="639" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A639" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B639" s="6">
-        <v>3.9999999999999998E-6</v>
+        <v>1.2E-5</v>
       </c>
       <c r="C639" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D639" t="s">
         <v>6</v>
@@ -13487,7 +13478,7 @@
         <v>16</v>
       </c>
       <c r="G639" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H639" t="s">
         <v>316</v>
@@ -13495,289 +13486,312 @@
     </row>
     <row r="640" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A640" t="s">
+        <v>43</v>
+      </c>
+      <c r="B640" s="6">
+        <v>3.9999999999999998E-6</v>
+      </c>
+      <c r="C640" t="s">
+        <v>8</v>
+      </c>
+      <c r="D640" t="s">
+        <v>6</v>
+      </c>
+      <c r="F640" t="s">
+        <v>16</v>
+      </c>
+      <c r="G640" t="s">
+        <v>50</v>
+      </c>
+      <c r="H640" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="641" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A641" t="s">
         <v>195</v>
       </c>
-      <c r="B640" s="6">
-        <f>B634*-1/1000</f>
+      <c r="B641" s="6">
+        <f>B635*-1/1000</f>
         <v>-1.5E-3</v>
       </c>
-      <c r="C640" t="s">
+      <c r="C641" t="s">
         <v>131</v>
       </c>
-      <c r="D640" t="s">
+      <c r="D641" t="s">
         <v>49</v>
       </c>
-      <c r="F640" t="s">
-        <v>16</v>
-      </c>
-      <c r="G640" t="s">
+      <c r="F641" t="s">
+        <v>16</v>
+      </c>
+      <c r="G641" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="641" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A641" s="28" t="s">
+    <row r="642" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A642" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="B641">
-        <v>1</v>
-      </c>
-      <c r="C641" t="s">
-        <v>8</v>
-      </c>
-      <c r="D641" t="s">
-        <v>6</v>
-      </c>
-      <c r="F641" t="s">
-        <v>16</v>
-      </c>
-      <c r="G641" t="s">
+      <c r="B642">
+        <v>1</v>
+      </c>
+      <c r="C642" t="s">
+        <v>8</v>
+      </c>
+      <c r="D642" t="s">
+        <v>6</v>
+      </c>
+      <c r="F642" t="s">
+        <v>16</v>
+      </c>
+      <c r="G642" t="s">
         <v>98</v>
       </c>
-      <c r="H641" t="s">
+      <c r="H642" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="642" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A642" t="s">
+    <row r="643" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A643" t="s">
         <v>39</v>
       </c>
-      <c r="B642">
-        <v>1</v>
-      </c>
-      <c r="D642" t="s">
-        <v>6</v>
-      </c>
-      <c r="E642" t="s">
+      <c r="B643">
+        <v>1</v>
+      </c>
+      <c r="D643" t="s">
+        <v>6</v>
+      </c>
+      <c r="E643" t="s">
         <v>37</v>
       </c>
-      <c r="F642" t="s">
+      <c r="F643" t="s">
         <v>20</v>
       </c>
-      <c r="G642">
+      <c r="G643">
         <v>0</v>
       </c>
-      <c r="H642" t="s">
-        <v>283</v>
-      </c>
-      <c r="M642" t="s">
+      <c r="H643" t="s">
+        <v>284</v>
+      </c>
+      <c r="M643" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="644" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A644" s="1" t="s">
+    <row r="645" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A645" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B644" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="645" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A645" t="s">
-        <v>1</v>
-      </c>
-      <c r="B645">
-        <v>1</v>
+      <c r="B645" s="1" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="646" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A646" t="s">
-        <v>2</v>
-      </c>
-      <c r="B646" t="s">
-        <v>294</v>
+        <v>1</v>
+      </c>
+      <c r="B646">
+        <v>1</v>
       </c>
     </row>
     <row r="647" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A647" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B647" t="s">
-        <v>4</v>
+        <v>295</v>
       </c>
     </row>
     <row r="648" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A648" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B648" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="649" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A649" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B649" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="650" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A650" t="s">
-        <v>18</v>
-      </c>
-      <c r="B650" s="6" t="s">
-        <v>319</v>
+        <v>7</v>
+      </c>
+      <c r="B650" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="651" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A651" t="s">
+        <v>18</v>
+      </c>
+      <c r="B651" s="6" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="652" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A652" t="s">
         <v>9</v>
       </c>
-      <c r="B651" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="652" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A652" s="1" t="s">
+      <c r="B652" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="653" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A653" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="653" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A653" s="5" t="s">
+    <row r="654" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A654" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B653" s="5" t="s">
+      <c r="B654" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C653" s="5" t="s">
+      <c r="C654" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D653" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E653" s="5" t="s">
+      <c r="D654" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E654" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F653" s="5" t="s">
+      <c r="F654" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G653" s="5" t="s">
+      <c r="G654" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H653" s="5" t="s">
+      <c r="H654" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I653" s="5" t="s">
+      <c r="I654" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="J653" s="5" t="s">
+      <c r="J654" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="K653" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="L653" s="5" t="s">
+      <c r="K654" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="M653" s="5" t="s">
+      <c r="L654" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="M654" s="5" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="654" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A654" t="str">
-        <f>B644</f>
+    <row r="655" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A655" t="str">
+        <f>B645</f>
         <v>carbon dioxide, captured and stored, from a biomass fermentation plant</v>
       </c>
-      <c r="B654">
-        <v>1</v>
-      </c>
-      <c r="C654" t="s">
-        <v>8</v>
-      </c>
-      <c r="D654" t="s">
-        <v>6</v>
-      </c>
-      <c r="F654" t="s">
+      <c r="B655">
+        <v>1</v>
+      </c>
+      <c r="C655" t="s">
+        <v>8</v>
+      </c>
+      <c r="D655" t="s">
+        <v>6</v>
+      </c>
+      <c r="F655" t="s">
         <v>15</v>
       </c>
-      <c r="G654" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="655" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A655" t="s">
+      <c r="G655" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="656" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A656" t="s">
         <v>34</v>
       </c>
-      <c r="B655" s="23">
+      <c r="B656" s="23">
         <v>0.11</v>
       </c>
-      <c r="C655" t="s">
-        <v>8</v>
-      </c>
-      <c r="D655" t="s">
+      <c r="C656" t="s">
+        <v>8</v>
+      </c>
+      <c r="D656" t="s">
         <v>23</v>
       </c>
-      <c r="F655" t="s">
-        <v>16</v>
-      </c>
-      <c r="G655" t="s">
+      <c r="F656" t="s">
+        <v>16</v>
+      </c>
+      <c r="G656" t="s">
         <v>24</v>
       </c>
-      <c r="H655" t="s">
-        <v>310</v>
-      </c>
-      <c r="I655">
-        <v>5</v>
-      </c>
-      <c r="J655" s="23">
-        <f>B655</f>
+      <c r="H656" t="s">
+        <v>311</v>
+      </c>
+      <c r="I656">
+        <v>5</v>
+      </c>
+      <c r="J656" s="23">
+        <f>B656</f>
         <v>0.11</v>
       </c>
-      <c r="K655">
+      <c r="K656">
         <v>0.1</v>
       </c>
-      <c r="L655">
+      <c r="L656">
         <v>0.2</v>
       </c>
     </row>
-    <row r="656" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A656" s="28" t="s">
+    <row r="657" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A657" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="B656">
-        <v>1</v>
-      </c>
-      <c r="C656" t="s">
-        <v>8</v>
-      </c>
-      <c r="D656" t="s">
-        <v>6</v>
-      </c>
-      <c r="F656" t="s">
-        <v>16</v>
-      </c>
-      <c r="G656" t="s">
+      <c r="B657">
+        <v>1</v>
+      </c>
+      <c r="C657" t="s">
+        <v>8</v>
+      </c>
+      <c r="D657" t="s">
+        <v>6</v>
+      </c>
+      <c r="F657" t="s">
+        <v>16</v>
+      </c>
+      <c r="G657" t="s">
         <v>98</v>
       </c>
-      <c r="H656" t="s">
+      <c r="H657" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="657" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A657" t="s">
+    <row r="658" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A658" t="s">
         <v>39</v>
       </c>
-      <c r="B657">
-        <v>1</v>
-      </c>
-      <c r="D657" t="s">
-        <v>6</v>
-      </c>
-      <c r="E657" t="s">
+      <c r="B658">
+        <v>1</v>
+      </c>
+      <c r="D658" t="s">
+        <v>6</v>
+      </c>
+      <c r="E658" t="s">
         <v>37</v>
       </c>
-      <c r="F657" t="s">
+      <c r="F658" t="s">
         <v>20</v>
       </c>
-      <c r="H657" t="s">
-        <v>283</v>
-      </c>
-      <c r="M657" t="s">
+      <c r="H658" t="s">
+        <v>284</v>
+      </c>
+      <c r="M658" t="s">
         <v>183</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V620" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:V621" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
